--- a/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
+++ b/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rod\Desktop\EPS\EI\US EPS InputData reference files\InputData\elec\BCpUC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\elec\BCpUC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{FCC0A0F8-0EC6-4D16-892B-1D005881481C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F999CC8B-F294-4ECE-B7CB-A5D9E6F95452}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D5D59D-3B3B-4355-BE1D-2AA5A11B072E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="839" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="839" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -25,20 +25,14 @@
     <definedName name="cpi_2020_to_2012">About!$A$50</definedName>
     <definedName name="cpi_2022_to_2012">About!$A$52</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -46,12 +40,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="151">
   <si>
-    <t>BCpUC Battery Cost per Unit Capacity</t>
+    <t>Year</t>
   </si>
   <si>
-    <t>BCpUC Battery Balance of System Cost as Share of First Year Cost</t>
+    <t>$/kWh</t>
   </si>
   <si>
     <t>Sources:</t>
@@ -66,10 +60,10 @@
     <t>The Economics of Grid Defection</t>
   </si>
   <si>
-    <t>http://www.rmi.org/electricity_grid_defection</t>
+    <t>Page 61, First Table, "Li-ion Battery Capital Cost"</t>
   </si>
   <si>
-    <t>Page 61, First Table, "Li-ion Battery Capital Cost"</t>
+    <t>http://www.rmi.org/electricity_grid_defection</t>
   </si>
   <si>
     <t>2010 Battery Costs per kW</t>
@@ -87,25 +81,97 @@
     <t>Page B-45, Table B-28</t>
   </si>
   <si>
-    <t>Capital Costs</t>
+    <t>Battery Cost ($/MW)</t>
   </si>
   <si>
-    <t>National Renewable Energy Laboratory</t>
+    <t>Note:</t>
   </si>
   <si>
-    <t>Annual Technology Baseline</t>
+    <t>See "cpi.xlsx" in the InputData folder for source information.</t>
   </si>
   <si>
-    <t>https://atb.nrel.gov/electricity/2024/data</t>
+    <t>BCpUC Battery Cost per Unit Capacity</t>
   </si>
   <si>
-    <t>Utility-Scale Battery Storage tab, CAPEX, Moderate scenario</t>
+    <t>learning.</t>
+  </si>
+  <si>
+    <t>Balance of System</t>
+  </si>
+  <si>
+    <t>Table 3. Detailed Cost Breakdown for a 60-MW U.S. Li-ion Standalone Storage System with Durations of 0.5–4 Hours</t>
+  </si>
+  <si>
+    <t>60-MW, 4-hour Duration, 240-MWh</t>
+  </si>
+  <si>
+    <t>60-MW, 2-hour Duration, 120-MWh</t>
+  </si>
+  <si>
+    <t>60-MW, 1-hour Duration, 60-MWh</t>
+  </si>
+  <si>
+    <t>60-MW, 0.5-hour Duration, 30-MWh</t>
+  </si>
+  <si>
+    <t>Li-ion battery</t>
+  </si>
+  <si>
+    <t>Battery central inverter</t>
+  </si>
+  <si>
+    <t>Structural BOS</t>
+  </si>
+  <si>
+    <t>Electrical BOS</t>
+  </si>
+  <si>
+    <t>EPC overhead</t>
+  </si>
+  <si>
+    <t>Sales tax</t>
+  </si>
+  <si>
+    <t>∑ EPC cost</t>
+  </si>
+  <si>
+    <t>Land acquisition</t>
+  </si>
+  <si>
+    <t>Permitting fee</t>
+  </si>
+  <si>
+    <t>Interconnection fee</t>
+  </si>
+  <si>
+    <t>Contingency</t>
+  </si>
+  <si>
+    <t>Developer overhead</t>
+  </si>
+  <si>
+    <t>EPC/developer net profit</t>
+  </si>
+  <si>
+    <t>∑ Developer cost</t>
+  </si>
+  <si>
+    <t>Total Cost ($)</t>
+  </si>
+  <si>
+    <t>$/W</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Model Component</t>
+  </si>
+  <si>
+    <t>Installation labor &amp; equipment</t>
   </si>
   <si>
     <t>Balance of System Costs</t>
-  </si>
-  <si>
-    <t>2018 U.S. Utility-Scale Photovoltaics Plus-Energy Storage System Costs Benchmark</t>
   </si>
   <si>
     <t>https://www.nrel.gov/docs/fy19osti/71714.pdf</t>
@@ -114,28 +180,19 @@
     <t>Page 12, Table 3</t>
   </si>
   <si>
-    <t>Note:</t>
+    <t>National Renewable Energy Laboratory</t>
   </si>
   <si>
-    <t>Used to calculate battery storage deployment. Only the years of this time series</t>
+    <t>2018 U.S. Utility-Scale Photovoltaics Plus-Energy Storage System Costs Benchmark</t>
   </si>
   <si>
-    <t xml:space="preserve">provided via input data are used, and the remaining years are handled via endogenous </t>
+    <t>We use the largest (4-hour duration) for our estimate.</t>
   </si>
   <si>
-    <t>learning.</t>
+    <t>Balance of System (excl. sales tax)</t>
   </si>
   <si>
-    <t>We hard code all years of power costs, because the ATB data remains relatively constant</t>
-  </si>
-  <si>
-    <t>rather than declining with time. We do apply endogenous learning to the energy costs.</t>
-  </si>
-  <si>
-    <t>Balance of System</t>
-  </si>
-  <si>
-    <t>The "balance of system" should include the proportion ofcosts the utility must pay to purchase and</t>
+    <t>Sales tax on balance of system elements</t>
   </si>
   <si>
     <t>install the battery system, apart from the batteries themselves (and apart from sales</t>
@@ -144,37 +201,46 @@
     <t>tax on the batteries).  This includes the inverter, labor, etc.</t>
   </si>
   <si>
-    <t>We determine this value via calibration against ATB data.</t>
+    <t>Currency Adjustment</t>
   </si>
   <si>
-    <t>Currency Adjustment</t>
+    <t>2010 to 2012 USD</t>
   </si>
   <si>
     <t>We adjust currency using the following conversion factors:</t>
   </si>
   <si>
-    <t>2010 to 2012 USD</t>
+    <t>2018 $/W</t>
+  </si>
+  <si>
+    <t>2018 $/MW</t>
   </si>
   <si>
     <t>2018 to 2012 USD</t>
   </si>
   <si>
-    <t>2019 to 2012 USD</t>
+    <t>2012 $/MW</t>
+  </si>
+  <si>
+    <t>For the U.S. model, we assume the balance of system costs remain constant throughout the model run.</t>
+  </si>
+  <si>
+    <t>Techno-Economic Cost and Performance Parameters</t>
+  </si>
+  <si>
+    <t>Capital Costs</t>
+  </si>
+  <si>
+    <t>Annual Technology Baseline</t>
+  </si>
+  <si>
+    <t>Utility-Scale Battery Storage tab, CAPEX, Moderate scenario</t>
   </si>
   <si>
     <t>2020 to 2012 USD</t>
   </si>
   <si>
-    <t>2021 to 2012 USD</t>
-  </si>
-  <si>
-    <t>2022 to 2012 USD</t>
-  </si>
-  <si>
-    <t>See "cpi.xlsx" in the InputData folder for source information.</t>
-  </si>
-  <si>
-    <t>Assumed duration:</t>
+    <t>2019 to 2012 USD</t>
   </si>
   <si>
     <t>Utility-Scale Battery Storage</t>
@@ -204,9 +270,6 @@
     <t>Base Year:</t>
   </si>
   <si>
-    <t>All values are given in 2021 U.S. dollars, see references at the bottom of this worksheet for dollar year conversions where source dollar years don't match 2021.</t>
-  </si>
-  <si>
     <t>Utility Scale Battery Storage</t>
   </si>
   <si>
@@ -230,9 +293,6 @@
       </rPr>
       <t xml:space="preserve"> storage (4 hours)</t>
     </r>
-  </si>
-  <si>
-    <t>Reference: Battery Storage cost values from W. Cole and A. Karmakar, “Cost Projections for Utility-scale Battery Storage: 2023 Update,” NREL/TP-6A40-85332. Golden, CO: National Renewable Energy Laboratory. https://www.nrel.gov/docs/fy23osti/85332.pdf. Note that values are converted to 2021$ for the ATB.</t>
   </si>
   <si>
     <t>Capital Cost ($/kWh)</t>
@@ -316,13 +376,7 @@
     <t>Future Projections</t>
   </si>
   <si>
-    <t xml:space="preserve">All values are given in 2021 U.S. dollars, using the Consumer Price Index (BLS, 2022) for dollar year conversions. </t>
-  </si>
-  <si>
     <t>For 15-year technical life (values in 2021$):</t>
-  </si>
-  <si>
-    <t>Techno-Economic Cost and Performance Parameters</t>
   </si>
   <si>
     <t>Overnight Capital Cost ($/kW)</t>
@@ -394,130 +448,70 @@
     <t>Grid Connection Cost ($/kW)</t>
   </si>
   <si>
-    <t>Table 3. Detailed Cost Breakdown for a 60-MW U.S. Li-ion Standalone Storage System with Durations of 0.5–4 Hours</t>
+    <t>Battery Cost ($/MWh)</t>
   </si>
   <si>
-    <t>60-MW, 4-hour Duration, 240-MWh</t>
+    <t>Unit: Dmnl</t>
   </si>
   <si>
-    <t>60-MW, 2-hour Duration, 120-MWh</t>
+    <t>Assumed duration:</t>
   </si>
   <si>
-    <t>60-MW, 1-hour Duration, 60-MWh</t>
+    <t>BCpUC Battery Balance of System Cost as Share of First Year Cost</t>
   </si>
   <si>
-    <t>60-MW, 0.5-hour Duration, 30-MWh</t>
+    <t>https://atb.nrel.gov/electricity/2024/data</t>
   </si>
   <si>
-    <t>Model Component</t>
+    <t>2022 to 2012 USD</t>
   </si>
   <si>
-    <t>Total Cost ($)</t>
+    <t>2021 to 2012 USD</t>
   </si>
   <si>
-    <t>$/kWh</t>
+    <t>Used to calculate battery storage deployment. Only the years of this time series</t>
   </si>
   <si>
-    <t>$/W</t>
+    <t xml:space="preserve">provided via input data are used, and the remaining years are handled via endogenous </t>
   </si>
   <si>
-    <t>Total Cost</t>
+    <t>We hard code all years of power costs, because the ATB data remains relatively constant</t>
   </si>
   <si>
-    <t>Li-ion battery</t>
+    <t>rather than declining with time. We do apply endogenous learning to the energy costs.</t>
   </si>
   <si>
-    <t>Battery central inverter</t>
+    <t>The "balance of system" should include the proportion ofcosts the utility must pay to purchase and</t>
   </si>
   <si>
-    <t>Structural BOS</t>
+    <t>We determine this value via calibration against ATB data.</t>
   </si>
   <si>
-    <t>Electrical BOS</t>
-  </si>
-  <si>
-    <t>Installation labor &amp; equipment</t>
-  </si>
-  <si>
-    <t>EPC overhead</t>
-  </si>
-  <si>
-    <t>Sales tax</t>
-  </si>
-  <si>
-    <t>∑ EPC cost</t>
-  </si>
-  <si>
-    <t>Land acquisition</t>
-  </si>
-  <si>
-    <t>Permitting fee</t>
-  </si>
-  <si>
-    <t>Interconnection fee</t>
-  </si>
-  <si>
-    <t>Contingency</t>
-  </si>
-  <si>
-    <t>Developer overhead</t>
-  </si>
-  <si>
-    <t>EPC/developer net profit</t>
-  </si>
-  <si>
-    <t>∑ Developer cost</t>
-  </si>
-  <si>
-    <t>We use the largest (4-hour duration) for our estimate.</t>
-  </si>
-  <si>
-    <t>Balance of System (excl. sales tax)</t>
-  </si>
-  <si>
-    <t>2018 $/W</t>
-  </si>
-  <si>
-    <t>Sales tax on balance of system elements</t>
-  </si>
-  <si>
-    <t>2018 $/MW</t>
-  </si>
-  <si>
-    <t>2012 $/MW</t>
-  </si>
-  <si>
-    <t>For the U.S. model, we assume the balance of system costs remain constant throughout the model run.</t>
+    <t>Raw Data (2022 $)</t>
   </si>
   <si>
     <t>Time (Year)</t>
   </si>
   <si>
-    <t>Battery Energy Cost per Unit Capacity : NDC</t>
+    <t>2021 (from 2023 ATB)</t>
   </si>
   <si>
-    <t>Battery Power Cost per Unit Capacity : NDC</t>
+    <t>All values are given in 2022 U.S. dollars except 2021 data.</t>
   </si>
   <si>
-    <t>Raw Data (2022 $)</t>
+    <t>Reference: Battery Storage cost values from W. Cole and A. Karmakar, “Cost Projections for Utility-scale Battery Storage: 2023 Update,” NREL/TP-6A40-85332. Golden, CO: National Renewable Energy Laboratory. https://www.nrel.gov/docs/fy23osti/85332.pdf.</t>
   </si>
   <si>
-    <t>2022 to 2013 costs</t>
+    <t xml:space="preserve">All values are given in 2022 U.S. dollars except for 2021 values from ATB 2023 </t>
   </si>
   <si>
-    <t>Year</t>
+    <t>Battery Energy Cost per Unit Capacity : test</t>
   </si>
   <si>
-    <t>Battery Cost ($/MWh)</t>
+    <t>2022 to 2012 costs</t>
   </si>
   <si>
-    <t>Battery Cost ($/MW)</t>
-  </si>
-  <si>
-    <t>Unit: Dmnl</t>
-  </si>
-  <si>
-    <t>Percent of First Year Total Costs</t>
+    <t>Battery Power Cost per Unit Capacity : test</t>
   </si>
 </sst>
 </file>
@@ -534,7 +528,7 @@
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1974,6 +1968,12 @@
     <xf numFmtId="5" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2025,6 +2025,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2049,6 +2050,7 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2085,25 +2087,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Currency" xfId="8" builtinId="4"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Footnotes: top row" xfId="7" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Header: bottom row" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
-    <cellStyle name="Moneda" xfId="8" builtinId="4"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Parent row" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Porcentaje" xfId="9" builtinId="5"/>
+    <cellStyle name="Percent" xfId="9" builtinId="5"/>
     <cellStyle name="Table title" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2127,7 +2121,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2230,85 +2224,85 @@
                   <c:v>303546</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>277345</c:v>
+                  <c:v>274986</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>256728</c:v>
+                  <c:v>253296</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>240275</c:v>
+                  <c:v>236734</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>226464</c:v>
+                  <c:v>223030</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>214618</c:v>
+                  <c:v>211554</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>204553</c:v>
+                  <c:v>201954</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>196075</c:v>
+                  <c:v>193764</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>188655</c:v>
+                  <c:v>186541</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>182183</c:v>
+                  <c:v>180196</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>176401</c:v>
+                  <c:v>174552</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>171611</c:v>
+                  <c:v>169876</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>167430</c:v>
+                  <c:v>165776</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>163809</c:v>
+                  <c:v>162216</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>160633</c:v>
+                  <c:v>159077</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>157780</c:v>
+                  <c:v>156257</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>155218</c:v>
+                  <c:v>153722</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>152921</c:v>
+                  <c:v>151442</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>150890</c:v>
+                  <c:v>149428</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>149018</c:v>
+                  <c:v>147587</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>147310</c:v>
+                  <c:v>145898</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>145744</c:v>
+                  <c:v>144352</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>144287</c:v>
+                  <c:v>142921</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>142963</c:v>
+                  <c:v>141617</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>141726</c:v>
+                  <c:v>140396</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>140576</c:v>
+                  <c:v>139257</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>139495</c:v>
+                  <c:v>138188</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>138485</c:v>
+                  <c:v>137190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2600,6 +2594,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2607,7 +2602,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2645,7 +2639,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3118,6 +3112,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3125,7 +3120,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4616,24 +4610,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B55"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:C55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
     <col min="2" max="2" width="67.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -4641,242 +4635,246 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="4">
         <v>2014</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>2013</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>2024</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>2018</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1.0549999999999999</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="38">
         <v>0.9143273584567535</v>
       </c>
       <c r="B48" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>0.89805481563188172</v>
       </c>
       <c r="B49" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="38">
         <v>0.88711067149387013</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="38">
         <v>0.84730412960844359</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>135</v>
+      </c>
+      <c r="C51">
+        <f>cpi_2022_to_2012/A51</f>
+        <v>0.92590251319813455</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="38">
         <v>0.78452102304761584</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="B55">
         <v>4</v>
@@ -4895,7 +4893,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734360E0-DC8F-4FFB-9748-D4950767514E}">
   <dimension ref="A1:DD222"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" customWidth="1"/>
     <col min="4" max="4" width="36.42578125" customWidth="1"/>
@@ -4906,25 +4904,25 @@
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:108" s="40" customFormat="1" ht="18">
-      <c r="A1" s="179" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="179"/>
-      <c r="I1" s="179"/>
-      <c r="J1" s="179"/>
-      <c r="K1" s="179"/>
+    <row r="1" spans="1:108" s="40" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="165" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="165"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
       <c r="M1" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="B2"/>
       <c r="C2"/>
@@ -4937,7 +4935,7 @@
       <c r="J2" s="41"/>
       <c r="K2" s="41"/>
       <c r="L2" s="42" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="M2" s="41"/>
       <c r="N2" s="41"/>
@@ -5036,7 +5034,7 @@
       <c r="DC2" s="41"/>
       <c r="DD2" s="41"/>
     </row>
-    <row r="3" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1">
+    <row r="3" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3"/>
       <c r="B3"/>
       <c r="C3"/>
@@ -5044,19 +5042,19 @@
       <c r="E3"/>
       <c r="F3"/>
       <c r="L3" s="43" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="44"/>
-      <c r="L4" s="159" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:108" ht="14.85" customHeight="1">
-      <c r="L5" s="160"/>
-    </row>
-    <row r="6" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1">
+      <c r="L4" s="166" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:108" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L5" s="167"/>
+    </row>
+    <row r="6" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H6" s="45"/>
       <c r="I6" s="46"/>
       <c r="J6" s="46"/>
@@ -5082,27 +5080,27 @@
       <c r="AE6" s="47"/>
       <c r="AF6" s="48"/>
     </row>
-    <row r="7" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1">
+    <row r="7" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="155" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="155"/>
-      <c r="K7" s="155"/>
-      <c r="L7" s="155"/>
-      <c r="M7" s="155"/>
-      <c r="N7" s="155"/>
-      <c r="O7" s="155"/>
-      <c r="P7" s="155"/>
-      <c r="Q7" s="155"/>
+        <v>72</v>
+      </c>
+      <c r="C7" s="161" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="161"/>
+      <c r="E7" s="161"/>
+      <c r="F7" s="161"/>
+      <c r="G7" s="161"/>
+      <c r="H7" s="161"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="161"/>
+      <c r="K7" s="161"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
+      <c r="N7" s="161"/>
+      <c r="O7" s="161"/>
+      <c r="P7" s="161"/>
+      <c r="Q7" s="161"/>
       <c r="R7" s="50"/>
       <c r="S7" s="50"/>
       <c r="T7" s="50"/>
@@ -5115,67 +5113,67 @@
       <c r="AA7" s="51"/>
       <c r="AB7" s="48"/>
     </row>
-    <row r="8" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1">
+    <row r="8" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="O8" s="52"/>
     </row>
-    <row r="9" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1">
+    <row r="9" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9"/>
-      <c r="B9" s="161" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="162" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="163"/>
-      <c r="F9" s="164"/>
-      <c r="G9" s="165">
-        <v>2021</v>
-      </c>
-      <c r="H9" s="166"/>
-      <c r="I9" s="166"/>
-      <c r="J9" s="166"/>
-      <c r="K9" s="180"/>
-      <c r="L9" s="180"/>
-    </row>
-    <row r="10" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B10" s="161"/>
+      <c r="B9" s="168" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="169" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="G9" s="172">
+        <v>2022</v>
+      </c>
+      <c r="H9" s="173"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="174"/>
+      <c r="L9" s="174"/>
+    </row>
+    <row r="10" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="168"/>
       <c r="D10" s="53" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="J10" s="52"/>
     </row>
-    <row r="11" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B11" s="161"/>
-      <c r="D11" s="167" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="168"/>
-      <c r="F11" s="168"/>
-      <c r="G11" s="168"/>
-      <c r="H11" s="168"/>
-      <c r="I11" s="168"/>
-      <c r="J11" s="168"/>
-      <c r="K11" s="168"/>
-      <c r="L11" s="168"/>
+    <row r="11" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="168"/>
+      <c r="D11" s="175" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="176"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="176"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="176"/>
       <c r="W11" s="54"/>
       <c r="X11" s="55"/>
       <c r="Y11" s="55"/>
       <c r="Z11" s="55"/>
       <c r="AA11" s="55"/>
     </row>
-    <row r="12" spans="1:108" s="40" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
-      <c r="B12" s="161"/>
-      <c r="D12" s="169" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="170"/>
-      <c r="F12" s="170"/>
-      <c r="G12" s="170"/>
-      <c r="H12" s="170"/>
-      <c r="I12" s="170"/>
-      <c r="J12" s="170"/>
-      <c r="K12" s="170"/>
-      <c r="L12" s="171"/>
+    <row r="12" spans="1:108" s="40" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="168"/>
+      <c r="D12" s="177" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="178"/>
+      <c r="F12" s="178"/>
+      <c r="G12" s="178"/>
+      <c r="H12" s="178"/>
+      <c r="I12" s="178"/>
+      <c r="J12" s="178"/>
+      <c r="K12" s="178"/>
+      <c r="L12" s="179"/>
       <c r="M12" s="56"/>
       <c r="W12" s="54"/>
       <c r="X12" s="55"/>
@@ -5183,79 +5181,79 @@
       <c r="Z12" s="55"/>
       <c r="AA12" s="55"/>
     </row>
-    <row r="13" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B13" s="161"/>
-      <c r="D13" s="172"/>
-      <c r="E13" s="173"/>
-      <c r="F13" s="173"/>
-      <c r="G13" s="173"/>
-      <c r="H13" s="173"/>
-      <c r="I13" s="173"/>
-      <c r="J13" s="173"/>
-      <c r="K13" s="173"/>
-      <c r="L13" s="174"/>
+    <row r="13" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="168"/>
+      <c r="D13" s="180"/>
+      <c r="E13" s="181"/>
+      <c r="F13" s="181"/>
+      <c r="G13" s="181"/>
+      <c r="H13" s="181"/>
+      <c r="I13" s="181"/>
+      <c r="J13" s="181"/>
+      <c r="K13" s="181"/>
+      <c r="L13" s="182"/>
       <c r="W13" s="54"/>
       <c r="X13" s="55"/>
       <c r="Y13" s="55"/>
       <c r="Z13" s="55"/>
       <c r="AA13" s="55"/>
     </row>
-    <row r="14" spans="1:108" ht="37.35" customHeight="1">
-      <c r="B14" s="161"/>
-    </row>
-    <row r="15" spans="1:108">
-      <c r="B15" s="161"/>
-      <c r="C15" s="175" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="175"/>
-      <c r="E15" s="175"/>
-      <c r="F15" s="175"/>
-      <c r="G15" s="175"/>
-      <c r="H15" s="175"/>
-      <c r="I15" s="175"/>
-      <c r="J15" s="175"/>
-      <c r="K15" s="175"/>
-      <c r="L15" s="175"/>
-      <c r="M15" s="175"/>
-      <c r="N15" s="175"/>
-      <c r="O15" s="175"/>
-      <c r="P15" s="175"/>
+    <row r="14" spans="1:108" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="168"/>
+    </row>
+    <row r="15" spans="1:108" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="168"/>
+      <c r="C15" s="183" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="183"/>
+      <c r="E15" s="183"/>
+      <c r="F15" s="183"/>
+      <c r="G15" s="183"/>
+      <c r="H15" s="183"/>
+      <c r="I15" s="183"/>
+      <c r="J15" s="183"/>
+      <c r="K15" s="183"/>
+      <c r="L15" s="183"/>
+      <c r="M15" s="183"/>
+      <c r="N15" s="183"/>
+      <c r="O15" s="183"/>
+      <c r="P15" s="183"/>
       <c r="Q15" s="57"/>
     </row>
-    <row r="16" spans="1:108">
-      <c r="B16" s="161"/>
-      <c r="C16" s="175"/>
-      <c r="D16" s="175"/>
-      <c r="E16" s="175"/>
-      <c r="F16" s="175"/>
-      <c r="G16" s="175"/>
-      <c r="H16" s="175"/>
-      <c r="I16" s="175"/>
-      <c r="J16" s="175"/>
-      <c r="K16" s="175"/>
-      <c r="L16" s="175"/>
-      <c r="M16" s="175"/>
-      <c r="N16" s="175"/>
-      <c r="O16" s="175"/>
-      <c r="P16" s="175"/>
-    </row>
-    <row r="17" spans="2:39" ht="15" customHeight="1">
-      <c r="B17" s="161"/>
+    <row r="16" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="B16" s="168"/>
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+      <c r="F16" s="183"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="183"/>
+      <c r="I16" s="183"/>
+      <c r="J16" s="183"/>
+      <c r="K16" s="183"/>
+      <c r="L16" s="183"/>
+      <c r="M16" s="183"/>
+      <c r="N16" s="183"/>
+      <c r="O16" s="183"/>
+      <c r="P16" s="183"/>
+    </row>
+    <row r="17" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="168"/>
       <c r="C17" s="58"/>
-      <c r="D17" s="152" t="s">
-        <v>56</v>
+      <c r="D17" s="158" t="s">
+        <v>78</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="2:39" ht="15" customHeight="1">
-      <c r="B18" s="161"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="168"/>
       <c r="C18" s="58"/>
-      <c r="D18" s="153"/>
-      <c r="F18" s="1">
-        <v>2021</v>
+      <c r="D18" s="159"/>
+      <c r="F18" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="G18" s="1">
         <v>2022</v>
@@ -5345,12 +5343,12 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:39" ht="15" customHeight="1">
-      <c r="B19" s="161"/>
+    <row r="19" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="168"/>
       <c r="C19" s="58"/>
-      <c r="D19" s="153"/>
+      <c r="D19" s="159"/>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F19" s="59">
         <v>322.051049922</v>
@@ -5443,12 +5441,12 @@
         <v>129.15171555556242</v>
       </c>
     </row>
-    <row r="20" spans="2:39" ht="15" customHeight="1">
-      <c r="B20" s="161"/>
+    <row r="20" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="168"/>
       <c r="C20" s="58"/>
-      <c r="D20" s="154"/>
+      <c r="D20" s="160"/>
       <c r="E20" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="F20" s="59">
         <v>322.051049922</v>
@@ -5541,12 +5539,12 @@
         <v>157.23705301149212</v>
       </c>
     </row>
-    <row r="21" spans="2:39" ht="15" customHeight="1">
-      <c r="B21" s="161"/>
+    <row r="21" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="168"/>
       <c r="C21" s="58"/>
-      <c r="D21" s="154"/>
+      <c r="D21" s="160"/>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="F21" s="59">
         <v>322.051049922</v>
@@ -5639,10 +5637,10 @@
         <v>274.95897351378562</v>
       </c>
     </row>
-    <row r="22" spans="2:39" ht="15" customHeight="1">
-      <c r="B22" s="161"/>
+    <row r="22" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="168"/>
       <c r="C22" s="58"/>
-      <c r="D22" s="154"/>
+      <c r="D22" s="160"/>
       <c r="F22" s="60"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -5674,21 +5672,21 @@
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
     </row>
-    <row r="23" spans="2:39" ht="15" customHeight="1">
-      <c r="B23" s="161"/>
+    <row r="23" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="168"/>
       <c r="C23" s="58"/>
-      <c r="D23" s="154"/>
+      <c r="D23" s="160"/>
       <c r="E23" s="1" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="F23" s="60"/>
     </row>
-    <row r="24" spans="2:39" ht="15" customHeight="1">
-      <c r="B24" s="161"/>
+    <row r="24" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="168"/>
       <c r="C24" s="58"/>
-      <c r="D24" s="154"/>
-      <c r="F24" s="1">
-        <v>2021</v>
+      <c r="D24" s="160"/>
+      <c r="F24" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="G24" s="1">
         <v>2022</v>
@@ -5778,12 +5776,12 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="25" spans="2:39" ht="15" customHeight="1">
-      <c r="B25" s="161"/>
+    <row r="25" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="168"/>
       <c r="C25" s="58"/>
-      <c r="D25" s="154"/>
+      <c r="D25" s="160"/>
       <c r="E25" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F25" s="59">
         <v>299.04780031199999</v>
@@ -5876,12 +5874,12 @@
         <v>118.54336408357527</v>
       </c>
     </row>
-    <row r="26" spans="2:39" ht="15" customHeight="1">
-      <c r="B26" s="161"/>
+    <row r="26" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="168"/>
       <c r="C26" s="58"/>
-      <c r="D26" s="154"/>
+      <c r="D26" s="160"/>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="F26" s="59">
         <v>299.04780031199999</v>
@@ -5974,12 +5972,12 @@
         <v>270.30971238933148</v>
       </c>
     </row>
-    <row r="27" spans="2:39" ht="15" customHeight="1">
-      <c r="B27" s="161"/>
+    <row r="27" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="168"/>
       <c r="C27" s="58"/>
-      <c r="D27" s="154"/>
+      <c r="D27" s="160"/>
       <c r="E27" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="F27" s="59">
         <v>299.04780031199999</v>
@@ -6072,8 +6070,8 @@
         <v>291.72086922260991</v>
       </c>
     </row>
-    <row r="28" spans="2:39" ht="15" customHeight="1">
-      <c r="B28" s="161"/>
+    <row r="28" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="168"/>
       <c r="C28" s="58"/>
       <c r="D28" s="58"/>
       <c r="G28" s="5"/>
@@ -6110,12 +6108,12 @@
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
     </row>
-    <row r="29" spans="2:39" ht="15" customHeight="1">
-      <c r="B29" s="161"/>
+    <row r="29" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="168"/>
       <c r="C29" s="58"/>
       <c r="D29" s="58"/>
       <c r="E29" s="1" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="5"/>
@@ -6152,8 +6150,8 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
     </row>
-    <row r="30" spans="2:39" ht="15" customHeight="1" thickBot="1">
-      <c r="B30" s="161"/>
+    <row r="30" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="168"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
       <c r="E30" s="1"/>
@@ -6192,26 +6190,26 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
     </row>
-    <row r="31" spans="2:39" ht="15" customHeight="1" thickBot="1">
-      <c r="B31" s="161"/>
+    <row r="31" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="168"/>
       <c r="C31" s="58"/>
-      <c r="D31" s="153" t="s">
-        <v>63</v>
+      <c r="D31" s="159" t="s">
+        <v>85</v>
       </c>
       <c r="E31" s="61" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="F31" s="62" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G31" s="62" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H31" s="62" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="I31" s="63" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="64"/>
@@ -6244,24 +6242,24 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
     </row>
-    <row r="32" spans="2:39" ht="15" customHeight="1">
-      <c r="B32" s="161"/>
+    <row r="32" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="168"/>
       <c r="C32" s="58"/>
-      <c r="D32" s="153"/>
+      <c r="D32" s="159"/>
       <c r="E32" s="66" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F32" s="67" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="G32" s="67" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="H32" s="67" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I32" s="68" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="64"/>
@@ -6294,24 +6292,24 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
     </row>
-    <row r="33" spans="2:74" ht="15" customHeight="1">
-      <c r="B33" s="161"/>
+    <row r="33" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="168"/>
       <c r="C33" s="58"/>
-      <c r="D33" s="153"/>
+      <c r="D33" s="159"/>
       <c r="E33" s="69" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F33" s="70" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="G33" s="70" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="H33" s="70" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I33" s="71" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="64"/>
@@ -6344,24 +6342,24 @@
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
     </row>
-    <row r="34" spans="2:74" ht="15" customHeight="1">
-      <c r="B34" s="161"/>
+    <row r="34" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="168"/>
       <c r="C34" s="58"/>
-      <c r="D34" s="153"/>
+      <c r="D34" s="159"/>
       <c r="E34" s="72" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F34" s="73" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="G34" s="73" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="H34" s="73" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I34" s="74" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="64"/>
@@ -6394,24 +6392,24 @@
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
     </row>
-    <row r="35" spans="2:74" ht="15" customHeight="1">
-      <c r="B35" s="161"/>
+    <row r="35" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="168"/>
       <c r="C35" s="58"/>
-      <c r="D35" s="153"/>
+      <c r="D35" s="159"/>
       <c r="E35" s="69" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F35" s="70" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="G35" s="70" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="H35" s="70" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I35" s="71" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="64"/>
@@ -6444,24 +6442,24 @@
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
     </row>
-    <row r="36" spans="2:74" ht="15" customHeight="1" thickBot="1">
-      <c r="B36" s="161"/>
+    <row r="36" spans="2:74" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="168"/>
       <c r="C36" s="58"/>
-      <c r="D36" s="153"/>
+      <c r="D36" s="159"/>
       <c r="E36" s="75" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="F36" s="76" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G36" s="76" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="H36" s="76" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I36" s="77" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="64"/>
@@ -6494,7 +6492,7 @@
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
     </row>
-    <row r="37" spans="2:74" ht="15" customHeight="1">
+    <row r="37" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="58"/>
       <c r="D37" s="58"/>
       <c r="E37" s="1"/>
@@ -6533,24 +6531,24 @@
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
     </row>
-    <row r="38" spans="2:74" s="40" customFormat="1" ht="14.25" customHeight="1">
-      <c r="C38" s="155" t="s">
-        <v>82</v>
-      </c>
-      <c r="D38" s="155"/>
-      <c r="E38" s="155"/>
-      <c r="F38" s="155"/>
-      <c r="G38" s="155"/>
-      <c r="H38" s="155"/>
-      <c r="I38" s="155"/>
-      <c r="J38" s="155"/>
-      <c r="K38" s="155"/>
-      <c r="L38" s="155"/>
-      <c r="M38" s="155"/>
-      <c r="N38" s="155"/>
-      <c r="O38" s="155"/>
-      <c r="P38" s="155"/>
-      <c r="Q38" s="155"/>
+    <row r="38" spans="2:74" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="161" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="161"/>
+      <c r="E38" s="161"/>
+      <c r="F38" s="161"/>
+      <c r="G38" s="161"/>
+      <c r="H38" s="161"/>
+      <c r="I38" s="161"/>
+      <c r="J38" s="161"/>
+      <c r="K38" s="161"/>
+      <c r="L38" s="161"/>
+      <c r="M38" s="161"/>
+      <c r="N38" s="161"/>
+      <c r="O38" s="161"/>
+      <c r="P38" s="161"/>
+      <c r="Q38" s="161"/>
       <c r="R38" s="50"/>
       <c r="S38" s="50"/>
       <c r="T38" s="50"/>
@@ -6579,20 +6577,20 @@
       <c r="AQ38" s="78"/>
       <c r="AR38" s="78"/>
     </row>
-    <row r="39" spans="2:74" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1"/>
-    <row r="40" spans="2:74" ht="15.75" thickBot="1">
+    <row r="39" spans="2:74" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D40" s="53" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="2:74">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="41" spans="2:74" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="2:74">
-      <c r="G42" s="1">
-        <v>2021</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="G42" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="H42" s="1">
         <v>2022</v>
@@ -6682,18 +6680,18 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="43" spans="2:74" ht="15" customHeight="1">
-      <c r="B43" s="157" t="s">
-        <v>85</v>
-      </c>
-      <c r="D43" s="152" t="s">
-        <v>86</v>
+    <row r="43" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43" s="158" t="s">
+        <v>106</v>
       </c>
       <c r="E43" s="79" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F43" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G43" s="81">
         <f>F19*2+F25</f>
@@ -6787,14 +6785,14 @@
         <v>376.84679519470012</v>
       </c>
     </row>
-    <row r="44" spans="2:74">
-      <c r="B44" s="157"/>
-      <c r="D44" s="153"/>
+    <row r="44" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B44" s="163"/>
+      <c r="D44" s="159"/>
       <c r="E44" s="82" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F44" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G44" s="81">
         <f t="shared" ref="G44:G45" si="0">F20*2+F26</f>
@@ -6888,14 +6886,14 @@
         <v>584.78381841231567</v>
       </c>
     </row>
-    <row r="45" spans="2:74">
-      <c r="B45" s="157"/>
-      <c r="D45" s="153"/>
+    <row r="45" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B45" s="163"/>
+      <c r="D45" s="159"/>
       <c r="E45" s="83" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F45" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G45" s="81">
         <f t="shared" si="0"/>
@@ -6989,14 +6987,14 @@
         <v>841.63881625018121</v>
       </c>
     </row>
-    <row r="46" spans="2:74">
-      <c r="B46" s="157"/>
-      <c r="D46" s="154"/>
+    <row r="46" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B46" s="163"/>
+      <c r="D46" s="160"/>
       <c r="E46" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F46" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G46" s="81">
         <f>F19*4+F25</f>
@@ -7123,14 +7121,14 @@
       <c r="BU46" s="5"/>
       <c r="BV46" s="5"/>
     </row>
-    <row r="47" spans="2:74">
-      <c r="B47" s="157"/>
-      <c r="D47" s="154"/>
+    <row r="47" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B47" s="163"/>
+      <c r="D47" s="160"/>
       <c r="E47" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F47" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G47" s="81">
         <f>F20*4+F26</f>
@@ -7257,14 +7255,14 @@
       <c r="BU47" s="5"/>
       <c r="BV47" s="5"/>
     </row>
-    <row r="48" spans="2:74">
-      <c r="B48" s="157"/>
-      <c r="D48" s="154"/>
+    <row r="48" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B48" s="163"/>
+      <c r="D48" s="160"/>
       <c r="E48" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F48" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G48" s="81">
         <f t="shared" ref="G48" si="1">F21*4+F27</f>
@@ -7391,14 +7389,14 @@
       <c r="BU48" s="5"/>
       <c r="BV48" s="5"/>
     </row>
-    <row r="49" spans="2:74">
-      <c r="B49" s="157"/>
-      <c r="D49" s="154"/>
+    <row r="49" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B49" s="163"/>
+      <c r="D49" s="160"/>
       <c r="E49" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F49" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G49" s="81">
         <f t="shared" ref="G49:G51" si="2">F19*6+F25</f>
@@ -7525,14 +7523,14 @@
       <c r="BU49" s="5"/>
       <c r="BV49" s="5"/>
     </row>
-    <row r="50" spans="2:74">
-      <c r="B50" s="157"/>
-      <c r="D50" s="154"/>
+    <row r="50" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B50" s="163"/>
+      <c r="D50" s="160"/>
       <c r="E50" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F50" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G50" s="81">
         <f t="shared" si="2"/>
@@ -7659,14 +7657,14 @@
       <c r="BU50" s="5"/>
       <c r="BV50" s="5"/>
     </row>
-    <row r="51" spans="2:74">
-      <c r="B51" s="157"/>
-      <c r="D51" s="154"/>
+    <row r="51" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B51" s="163"/>
+      <c r="D51" s="160"/>
       <c r="E51" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F51" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G51" s="81">
         <f t="shared" si="2"/>
@@ -7793,14 +7791,14 @@
       <c r="BU51" s="5"/>
       <c r="BV51" s="5"/>
     </row>
-    <row r="52" spans="2:74">
-      <c r="B52" s="157"/>
-      <c r="D52" s="154"/>
+    <row r="52" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B52" s="163"/>
+      <c r="D52" s="160"/>
       <c r="E52" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F52" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G52" s="81">
         <f t="shared" ref="G52:G54" si="3">F19*8+F25</f>
@@ -7927,14 +7925,14 @@
       <c r="BU52" s="5"/>
       <c r="BV52" s="5"/>
     </row>
-    <row r="53" spans="2:74">
-      <c r="B53" s="157"/>
-      <c r="D53" s="154"/>
+    <row r="53" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B53" s="163"/>
+      <c r="D53" s="160"/>
       <c r="E53" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F53" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G53" s="81">
         <f t="shared" si="3"/>
@@ -8061,14 +8059,14 @@
       <c r="BU53" s="5"/>
       <c r="BV53" s="5"/>
     </row>
-    <row r="54" spans="2:74">
-      <c r="B54" s="157"/>
-      <c r="D54" s="154"/>
+    <row r="54" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B54" s="163"/>
+      <c r="D54" s="160"/>
       <c r="E54" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F54" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G54" s="81">
         <f t="shared" si="3"/>
@@ -8195,14 +8193,14 @@
       <c r="BU54" s="5"/>
       <c r="BV54" s="5"/>
     </row>
-    <row r="55" spans="2:74">
-      <c r="B55" s="157"/>
-      <c r="D55" s="154"/>
+    <row r="55" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B55" s="163"/>
+      <c r="D55" s="160"/>
       <c r="E55" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="F55" s="80" t="s">
         <v>80</v>
-      </c>
-      <c r="F55" s="80" t="s">
-        <v>58</v>
       </c>
       <c r="G55" s="81">
         <f t="shared" ref="G55:G57" si="4">F19*10+F25</f>
@@ -8329,14 +8327,14 @@
       <c r="BU55" s="5"/>
       <c r="BV55" s="5"/>
     </row>
-    <row r="56" spans="2:74">
-      <c r="B56" s="157"/>
-      <c r="D56" s="154"/>
+    <row r="56" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B56" s="163"/>
+      <c r="D56" s="160"/>
       <c r="E56" s="79" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="F56" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G56" s="81">
         <f t="shared" si="4"/>
@@ -8463,14 +8461,14 @@
       <c r="BU56" s="5"/>
       <c r="BV56" s="5"/>
     </row>
-    <row r="57" spans="2:74">
-      <c r="B57" s="157"/>
-      <c r="D57" s="154"/>
+    <row r="57" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B57" s="163"/>
+      <c r="D57" s="160"/>
       <c r="E57" s="79" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="F57" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G57" s="81">
         <f t="shared" si="4"/>
@@ -8597,8 +8595,8 @@
       <c r="BU57" s="5"/>
       <c r="BV57" s="5"/>
     </row>
-    <row r="58" spans="2:74">
-      <c r="B58" s="157"/>
+    <row r="58" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B58" s="163"/>
       <c r="D58" s="58"/>
       <c r="E58" s="82"/>
       <c r="F58" s="82"/>
@@ -8666,8 +8664,8 @@
       <c r="BU58" s="5"/>
       <c r="BV58" s="5"/>
     </row>
-    <row r="59" spans="2:74">
-      <c r="B59" s="157"/>
+    <row r="59" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B59" s="163"/>
       <c r="D59" s="58"/>
       <c r="E59" s="82"/>
       <c r="F59" s="82"/>
@@ -8735,8 +8733,8 @@
       <c r="BU59" s="5"/>
       <c r="BV59" s="5"/>
     </row>
-    <row r="60" spans="2:74">
-      <c r="B60" s="157"/>
+    <row r="60" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B60" s="163"/>
       <c r="D60" s="58"/>
       <c r="E60" s="82"/>
       <c r="F60" s="82"/>
@@ -8804,13 +8802,13 @@
       <c r="BU60" s="5"/>
       <c r="BV60" s="5"/>
     </row>
-    <row r="61" spans="2:74">
-      <c r="B61" s="157"/>
+    <row r="61" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B61" s="163"/>
       <c r="D61" s="84"/>
       <c r="E61" s="82"/>
       <c r="F61" s="82"/>
-      <c r="G61" s="1">
-        <v>2021</v>
+      <c r="G61" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="H61" s="1">
         <v>2022</v>
@@ -8900,16 +8898,16 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="62" spans="2:74">
-      <c r="B62" s="157"/>
-      <c r="D62" s="152" t="s">
-        <v>87</v>
+    <row r="62" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B62" s="163"/>
+      <c r="D62" s="158" t="s">
+        <v>107</v>
       </c>
       <c r="E62" s="79" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F62" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G62" s="81">
         <f t="shared" ref="G62:G70" si="5">0.025*G43</f>
@@ -9003,14 +9001,14 @@
         <v>9.4211698798675041</v>
       </c>
     </row>
-    <row r="63" spans="2:74">
-      <c r="B63" s="157"/>
-      <c r="D63" s="153"/>
+    <row r="63" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B63" s="163"/>
+      <c r="D63" s="159"/>
       <c r="E63" s="82" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F63" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G63" s="81">
         <f t="shared" si="5"/>
@@ -9104,14 +9102,14 @@
         <v>14.619595460307892</v>
       </c>
     </row>
-    <row r="64" spans="2:74">
-      <c r="B64" s="157"/>
-      <c r="D64" s="153"/>
+    <row r="64" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B64" s="163"/>
+      <c r="D64" s="159"/>
       <c r="E64" s="83" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F64" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G64" s="81">
         <f t="shared" si="5"/>
@@ -9205,14 +9203,14 @@
         <v>21.04097040625453</v>
       </c>
     </row>
-    <row r="65" spans="2:74">
-      <c r="B65" s="157"/>
-      <c r="D65" s="154"/>
+    <row r="65" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B65" s="163"/>
+      <c r="D65" s="160"/>
       <c r="E65" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F65" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G65" s="81">
         <f t="shared" si="5"/>
@@ -9306,14 +9304,14 @@
         <v>15.878755657645625</v>
       </c>
     </row>
-    <row r="66" spans="2:74">
-      <c r="B66" s="157"/>
-      <c r="D66" s="154"/>
+    <row r="66" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B66" s="163"/>
+      <c r="D66" s="160"/>
       <c r="E66" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F66" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G66" s="81">
         <f t="shared" si="5"/>
@@ -9407,14 +9405,14 @@
         <v>22.4814481108825</v>
       </c>
     </row>
-    <row r="67" spans="2:74">
-      <c r="B67" s="157"/>
-      <c r="D67" s="154"/>
+    <row r="67" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B67" s="163"/>
+      <c r="D67" s="160"/>
       <c r="E67" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F67" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G67" s="81">
         <f t="shared" si="5"/>
@@ -9508,14 +9506,14 @@
         <v>34.78891908194381</v>
       </c>
     </row>
-    <row r="68" spans="2:74">
-      <c r="B68" s="157"/>
-      <c r="D68" s="154"/>
+    <row r="68" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B68" s="163"/>
+      <c r="D68" s="160"/>
       <c r="E68" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F68" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G68" s="81">
         <f t="shared" si="5"/>
@@ -9609,14 +9607,14 @@
         <v>22.336341435423748</v>
       </c>
     </row>
-    <row r="69" spans="2:74">
-      <c r="B69" s="157"/>
-      <c r="D69" s="154"/>
+    <row r="69" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B69" s="163"/>
+      <c r="D69" s="160"/>
       <c r="E69" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F69" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G69" s="81">
         <f t="shared" si="5"/>
@@ -9710,14 +9708,14 @@
         <v>30.343300761457108</v>
       </c>
     </row>
-    <row r="70" spans="2:74">
-      <c r="B70" s="157"/>
-      <c r="D70" s="154"/>
+    <row r="70" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B70" s="163"/>
+      <c r="D70" s="160"/>
       <c r="E70" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F70" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G70" s="81">
         <f t="shared" si="5"/>
@@ -9811,14 +9809,14 @@
         <v>48.536867757633097</v>
       </c>
     </row>
-    <row r="71" spans="2:74">
-      <c r="B71" s="157"/>
-      <c r="D71" s="154"/>
+    <row r="71" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B71" s="163"/>
+      <c r="D71" s="160"/>
       <c r="E71" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F71" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G71" s="81">
         <f t="shared" ref="G71:G76" si="6">0.025*G52</f>
@@ -9945,14 +9943,14 @@
       <c r="BU71" s="5"/>
       <c r="BV71" s="5"/>
     </row>
-    <row r="72" spans="2:74">
-      <c r="B72" s="157"/>
-      <c r="D72" s="154"/>
+    <row r="72" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B72" s="163"/>
+      <c r="D72" s="160"/>
       <c r="E72" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F72" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G72" s="81">
         <f t="shared" si="6"/>
@@ -10079,14 +10077,14 @@
       <c r="BU72" s="5"/>
       <c r="BV72" s="5"/>
     </row>
-    <row r="73" spans="2:74">
-      <c r="B73" s="157"/>
-      <c r="D73" s="154"/>
+    <row r="73" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B73" s="163"/>
+      <c r="D73" s="160"/>
       <c r="E73" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F73" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G73" s="81">
         <f t="shared" si="6"/>
@@ -10213,14 +10211,14 @@
       <c r="BU73" s="5"/>
       <c r="BV73" s="5"/>
     </row>
-    <row r="74" spans="2:74">
-      <c r="B74" s="157"/>
-      <c r="D74" s="154"/>
+    <row r="74" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B74" s="163"/>
+      <c r="D74" s="160"/>
       <c r="E74" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="F74" s="80" t="s">
         <v>80</v>
-      </c>
-      <c r="F74" s="80" t="s">
-        <v>58</v>
       </c>
       <c r="G74" s="81">
         <f t="shared" si="6"/>
@@ -10347,14 +10345,14 @@
       <c r="BU74" s="5"/>
       <c r="BV74" s="5"/>
     </row>
-    <row r="75" spans="2:74">
-      <c r="B75" s="157"/>
-      <c r="D75" s="154"/>
+    <row r="75" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B75" s="163"/>
+      <c r="D75" s="160"/>
       <c r="E75" s="79" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="F75" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G75" s="81">
         <f t="shared" si="6"/>
@@ -10481,14 +10479,14 @@
       <c r="BU75" s="5"/>
       <c r="BV75" s="5"/>
     </row>
-    <row r="76" spans="2:74">
-      <c r="B76" s="157"/>
-      <c r="D76" s="154"/>
+    <row r="76" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B76" s="163"/>
+      <c r="D76" s="160"/>
       <c r="E76" s="79" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="F76" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G76" s="81">
         <f t="shared" si="6"/>
@@ -10615,19 +10613,19 @@
       <c r="BU76" s="5"/>
       <c r="BV76" s="5"/>
     </row>
-    <row r="77" spans="2:74">
-      <c r="B77" s="157"/>
+    <row r="77" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B77" s="163"/>
       <c r="D77" s="84"/>
       <c r="E77" s="82"/>
       <c r="F77" s="82"/>
     </row>
-    <row r="78" spans="2:74">
-      <c r="B78" s="157"/>
+    <row r="78" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B78" s="163"/>
       <c r="D78" s="40"/>
       <c r="E78" s="85"/>
       <c r="F78" s="85"/>
-      <c r="G78" s="1">
-        <v>2021</v>
+      <c r="G78" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="H78" s="1">
         <v>2022</v>
@@ -10717,16 +10715,16 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="79" spans="2:74">
-      <c r="B79" s="157"/>
-      <c r="D79" s="152" t="s">
-        <v>88</v>
+    <row r="79" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B79" s="163"/>
+      <c r="D79" s="158" t="s">
+        <v>108</v>
       </c>
       <c r="E79" s="79" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F79" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G79" s="59">
         <v>0</v>
@@ -10820,14 +10818,14 @@
       </c>
       <c r="AO79" s="1"/>
     </row>
-    <row r="80" spans="2:74">
-      <c r="B80" s="157"/>
-      <c r="D80" s="153"/>
+    <row r="80" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B80" s="163"/>
+      <c r="D80" s="159"/>
       <c r="E80" s="82" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F80" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G80" s="59">
         <v>0</v>
@@ -10921,14 +10919,14 @@
       </c>
       <c r="AO80" s="1"/>
     </row>
-    <row r="81" spans="2:41">
-      <c r="B81" s="157"/>
-      <c r="D81" s="153"/>
+    <row r="81" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B81" s="163"/>
+      <c r="D81" s="159"/>
       <c r="E81" s="83" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F81" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G81" s="59">
         <v>0</v>
@@ -11022,14 +11020,14 @@
       </c>
       <c r="AO81" s="1"/>
     </row>
-    <row r="82" spans="2:41">
-      <c r="B82" s="158"/>
-      <c r="D82" s="154"/>
+    <row r="82" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B82" s="164"/>
+      <c r="D82" s="160"/>
       <c r="E82" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F82" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G82" s="59">
         <v>0</v>
@@ -11122,14 +11120,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:41">
-      <c r="B83" s="158"/>
-      <c r="D83" s="154"/>
+    <row r="83" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B83" s="164"/>
+      <c r="D83" s="160"/>
       <c r="E83" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F83" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G83" s="59">
         <v>0</v>
@@ -11222,14 +11220,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:41">
-      <c r="B84" s="158"/>
-      <c r="D84" s="154"/>
+    <row r="84" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B84" s="164"/>
+      <c r="D84" s="160"/>
       <c r="E84" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F84" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G84" s="59">
         <v>0</v>
@@ -11324,14 +11322,14 @@
       <c r="AK84" s="5"/>
       <c r="AL84" s="5"/>
     </row>
-    <row r="85" spans="2:41">
-      <c r="B85" s="158"/>
-      <c r="D85" s="154"/>
+    <row r="85" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B85" s="164"/>
+      <c r="D85" s="160"/>
       <c r="E85" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F85" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G85" s="59">
         <v>0</v>
@@ -11426,14 +11424,14 @@
       <c r="AK85" s="5"/>
       <c r="AL85" s="5"/>
     </row>
-    <row r="86" spans="2:41">
-      <c r="B86" s="158"/>
-      <c r="D86" s="154"/>
+    <row r="86" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B86" s="164"/>
+      <c r="D86" s="160"/>
       <c r="E86" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F86" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G86" s="59">
         <v>0</v>
@@ -11528,14 +11526,14 @@
       <c r="AK86" s="5"/>
       <c r="AL86" s="5"/>
     </row>
-    <row r="87" spans="2:41">
-      <c r="B87" s="158"/>
-      <c r="D87" s="154"/>
+    <row r="87" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B87" s="164"/>
+      <c r="D87" s="160"/>
       <c r="E87" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F87" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G87" s="59">
         <v>0</v>
@@ -11630,14 +11628,14 @@
       <c r="AK87" s="5"/>
       <c r="AL87" s="5"/>
     </row>
-    <row r="88" spans="2:41">
-      <c r="B88" s="158"/>
-      <c r="D88" s="154"/>
+    <row r="88" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B88" s="164"/>
+      <c r="D88" s="160"/>
       <c r="E88" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F88" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G88" s="59">
         <v>0</v>
@@ -11732,14 +11730,14 @@
       <c r="AK88" s="5"/>
       <c r="AL88" s="5"/>
     </row>
-    <row r="89" spans="2:41">
-      <c r="B89" s="158"/>
-      <c r="D89" s="154"/>
+    <row r="89" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B89" s="164"/>
+      <c r="D89" s="160"/>
       <c r="E89" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F89" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G89" s="59">
         <v>0</v>
@@ -11834,14 +11832,14 @@
       <c r="AK89" s="5"/>
       <c r="AL89" s="5"/>
     </row>
-    <row r="90" spans="2:41">
-      <c r="B90" s="158"/>
-      <c r="D90" s="154"/>
+    <row r="90" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B90" s="164"/>
+      <c r="D90" s="160"/>
       <c r="E90" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F90" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G90" s="59">
         <v>0</v>
@@ -11936,14 +11934,14 @@
       <c r="AK90" s="5"/>
       <c r="AL90" s="5"/>
     </row>
-    <row r="91" spans="2:41">
-      <c r="B91" s="158"/>
-      <c r="D91" s="154"/>
+    <row r="91" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B91" s="164"/>
+      <c r="D91" s="160"/>
       <c r="E91" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="F91" s="80" t="s">
         <v>80</v>
-      </c>
-      <c r="F91" s="80" t="s">
-        <v>58</v>
       </c>
       <c r="G91" s="59">
         <v>0</v>
@@ -12038,14 +12036,14 @@
       <c r="AK91" s="5"/>
       <c r="AL91" s="5"/>
     </row>
-    <row r="92" spans="2:41">
-      <c r="B92" s="158"/>
-      <c r="D92" s="154"/>
+    <row r="92" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B92" s="164"/>
+      <c r="D92" s="160"/>
       <c r="E92" s="79" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="F92" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G92" s="59">
         <v>0</v>
@@ -12140,14 +12138,14 @@
       <c r="AK92" s="5"/>
       <c r="AL92" s="5"/>
     </row>
-    <row r="93" spans="2:41">
-      <c r="B93" s="158"/>
-      <c r="D93" s="154"/>
+    <row r="93" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B93" s="164"/>
+      <c r="D93" s="160"/>
       <c r="E93" s="79" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="F93" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G93" s="59">
         <v>0</v>
@@ -12242,13 +12240,13 @@
       <c r="AK93" s="5"/>
       <c r="AL93" s="5"/>
     </row>
-    <row r="94" spans="2:41">
-      <c r="B94" s="158"/>
-    </row>
-    <row r="95" spans="2:41" ht="15" customHeight="1">
-      <c r="B95" s="158"/>
-      <c r="G95" s="1">
-        <v>2021</v>
+    <row r="94" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B94" s="164"/>
+    </row>
+    <row r="95" spans="2:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="164"/>
+      <c r="G95" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="H95" s="1">
         <v>2022</v>
@@ -12338,16 +12336,16 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="96" spans="2:41">
-      <c r="B96" s="158"/>
-      <c r="D96" s="152" t="s">
-        <v>89</v>
+    <row r="96" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B96" s="164"/>
+      <c r="D96" s="158" t="s">
+        <v>109</v>
       </c>
       <c r="E96" s="79" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F96" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G96" s="86">
         <v>0.85</v>
@@ -12440,14 +12438,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="97" spans="2:36">
-      <c r="B97" s="158"/>
-      <c r="D97" s="153"/>
+    <row r="97" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B97" s="164"/>
+      <c r="D97" s="159"/>
       <c r="E97" s="82" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F97" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G97" s="86">
         <v>0.85</v>
@@ -12540,14 +12538,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="98" spans="2:36">
-      <c r="B98" s="158"/>
-      <c r="D98" s="153"/>
+    <row r="98" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B98" s="164"/>
+      <c r="D98" s="159"/>
       <c r="E98" s="83" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F98" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G98" s="86">
         <v>0.85</v>
@@ -12640,14 +12638,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="99" spans="2:36">
-      <c r="B99" s="158"/>
-      <c r="D99" s="154"/>
+    <row r="99" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B99" s="164"/>
+      <c r="D99" s="160"/>
       <c r="E99" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F99" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G99" s="86">
         <v>0.85</v>
@@ -12740,14 +12738,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="100" spans="2:36">
-      <c r="B100" s="158"/>
-      <c r="D100" s="154"/>
+    <row r="100" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B100" s="164"/>
+      <c r="D100" s="160"/>
       <c r="E100" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F100" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G100" s="86">
         <v>0.85</v>
@@ -12840,14 +12838,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="101" spans="2:36">
-      <c r="B101" s="158"/>
-      <c r="D101" s="154"/>
+    <row r="101" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B101" s="164"/>
+      <c r="D101" s="160"/>
       <c r="E101" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F101" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G101" s="86">
         <v>0.85</v>
@@ -12940,14 +12938,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="102" spans="2:36">
-      <c r="B102" s="158"/>
-      <c r="D102" s="154"/>
+    <row r="102" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B102" s="164"/>
+      <c r="D102" s="160"/>
       <c r="E102" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F102" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G102" s="86">
         <v>0.85</v>
@@ -13040,14 +13038,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="103" spans="2:36">
-      <c r="B103" s="158"/>
-      <c r="D103" s="154"/>
+    <row r="103" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B103" s="164"/>
+      <c r="D103" s="160"/>
       <c r="E103" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F103" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G103" s="86">
         <v>0.85</v>
@@ -13140,14 +13138,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="104" spans="2:36">
-      <c r="B104" s="158"/>
-      <c r="D104" s="154"/>
+    <row r="104" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B104" s="164"/>
+      <c r="D104" s="160"/>
       <c r="E104" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F104" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G104" s="86">
         <v>0.85</v>
@@ -13240,14 +13238,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="105" spans="2:36">
-      <c r="B105" s="158"/>
-      <c r="D105" s="154"/>
+    <row r="105" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B105" s="164"/>
+      <c r="D105" s="160"/>
       <c r="E105" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F105" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G105" s="86">
         <v>0.85</v>
@@ -13340,14 +13338,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="106" spans="2:36">
-      <c r="B106" s="158"/>
-      <c r="D106" s="154"/>
+    <row r="106" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B106" s="164"/>
+      <c r="D106" s="160"/>
       <c r="E106" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F106" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G106" s="86">
         <v>0.85</v>
@@ -13440,14 +13438,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="107" spans="2:36">
-      <c r="B107" s="158"/>
-      <c r="D107" s="154"/>
+    <row r="107" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B107" s="164"/>
+      <c r="D107" s="160"/>
       <c r="E107" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F107" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G107" s="86">
         <v>0.85</v>
@@ -13540,15 +13538,15 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="108" spans="2:36">
-      <c r="B108" s="158"/>
-      <c r="D108" s="154"/>
+    <row r="108" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B108" s="164"/>
+      <c r="D108" s="160"/>
       <c r="E108" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="F108" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="F108" s="80" t="s">
-        <v>58</v>
-      </c>
       <c r="G108" s="86">
         <v>0.85</v>
       </c>
@@ -13640,14 +13638,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="109" spans="2:36">
-      <c r="B109" s="158"/>
-      <c r="D109" s="154"/>
+    <row r="109" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B109" s="164"/>
+      <c r="D109" s="160"/>
       <c r="E109" s="79" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="F109" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G109" s="86">
         <v>0.85</v>
@@ -13740,14 +13738,14 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="110" spans="2:36">
-      <c r="B110" s="158"/>
-      <c r="D110" s="154"/>
+    <row r="110" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B110" s="164"/>
+      <c r="D110" s="160"/>
       <c r="E110" s="79" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="F110" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G110" s="86">
         <v>0.85</v>
@@ -13840,13 +13838,13 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="111" spans="2:36">
-      <c r="B111" s="158"/>
-    </row>
-    <row r="112" spans="2:36">
-      <c r="B112" s="158"/>
-      <c r="G112" s="1">
-        <v>2021</v>
+    <row r="111" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B111" s="164"/>
+    </row>
+    <row r="112" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B112" s="164"/>
+      <c r="G112" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="H112" s="1">
         <v>2022</v>
@@ -13936,16 +13934,16 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="113" spans="2:36">
-      <c r="B113" s="158"/>
-      <c r="D113" s="152" t="s">
-        <v>90</v>
+    <row r="113" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B113" s="164"/>
+      <c r="D113" s="158" t="s">
+        <v>110</v>
       </c>
       <c r="E113" s="79" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F113" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G113" s="86">
         <f>2/24</f>
@@ -14039,14 +14037,14 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="114" spans="2:36">
-      <c r="B114" s="158"/>
-      <c r="D114" s="153"/>
+    <row r="114" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B114" s="164"/>
+      <c r="D114" s="159"/>
       <c r="E114" s="82" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F114" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G114" s="86">
         <f t="shared" ref="G114:G115" si="7">2/24</f>
@@ -14140,14 +14138,14 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="115" spans="2:36">
-      <c r="B115" s="158"/>
-      <c r="D115" s="153"/>
+    <row r="115" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B115" s="164"/>
+      <c r="D115" s="159"/>
       <c r="E115" s="83" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F115" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G115" s="86">
         <f t="shared" si="7"/>
@@ -14241,14 +14239,14 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="116" spans="2:36">
-      <c r="B116" s="158"/>
-      <c r="D116" s="154"/>
+    <row r="116" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B116" s="164"/>
+      <c r="D116" s="160"/>
       <c r="E116" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F116" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G116" s="86">
         <f>4/24</f>
@@ -14342,14 +14340,14 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="117" spans="2:36">
-      <c r="B117" s="158"/>
-      <c r="D117" s="154"/>
+    <row r="117" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B117" s="164"/>
+      <c r="D117" s="160"/>
       <c r="E117" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F117" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G117" s="86">
         <f t="shared" ref="G117:G118" si="8">4/24</f>
@@ -14443,14 +14441,14 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="118" spans="2:36">
-      <c r="B118" s="158"/>
-      <c r="D118" s="154"/>
+    <row r="118" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B118" s="164"/>
+      <c r="D118" s="160"/>
       <c r="E118" s="79" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F118" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G118" s="86">
         <f t="shared" si="8"/>
@@ -14544,14 +14542,14 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="119" spans="2:36">
-      <c r="B119" s="158"/>
-      <c r="D119" s="154"/>
+    <row r="119" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B119" s="164"/>
+      <c r="D119" s="160"/>
       <c r="E119" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F119" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G119" s="86">
         <f>6/24</f>
@@ -14645,14 +14643,14 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="120" spans="2:36">
-      <c r="B120" s="158"/>
-      <c r="D120" s="154"/>
+    <row r="120" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B120" s="164"/>
+      <c r="D120" s="160"/>
       <c r="E120" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F120" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G120" s="86">
         <f t="shared" ref="G120:G121" si="9">6/24</f>
@@ -14746,14 +14744,14 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="121" spans="2:36">
-      <c r="B121" s="158"/>
-      <c r="D121" s="154"/>
+    <row r="121" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B121" s="164"/>
+      <c r="D121" s="160"/>
       <c r="E121" s="79" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F121" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G121" s="86">
         <f t="shared" si="9"/>
@@ -14847,14 +14845,14 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="122" spans="2:36">
-      <c r="B122" s="158"/>
-      <c r="D122" s="154"/>
+    <row r="122" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B122" s="164"/>
+      <c r="D122" s="160"/>
       <c r="E122" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F122" s="80" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G122" s="86">
         <f>8/24</f>
@@ -14948,14 +14946,14 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="123" spans="2:36">
-      <c r="B123" s="158"/>
-      <c r="D123" s="154"/>
+    <row r="123" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B123" s="164"/>
+      <c r="D123" s="160"/>
       <c r="E123" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F123" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G123" s="86">
         <f t="shared" ref="G123:G124" si="10">8/24</f>
@@ -15049,14 +15047,14 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="124" spans="2:36">
-      <c r="B124" s="158"/>
-      <c r="D124" s="154"/>
+    <row r="124" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B124" s="164"/>
+      <c r="D124" s="160"/>
       <c r="E124" s="79" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F124" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G124" s="86">
         <f t="shared" si="10"/>
@@ -15150,14 +15148,14 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="125" spans="2:36">
-      <c r="B125" s="158"/>
-      <c r="D125" s="154"/>
+    <row r="125" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B125" s="164"/>
+      <c r="D125" s="160"/>
       <c r="E125" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="F125" s="80" t="s">
         <v>80</v>
-      </c>
-      <c r="F125" s="80" t="s">
-        <v>58</v>
       </c>
       <c r="G125" s="86">
         <f>10/24</f>
@@ -15251,14 +15249,14 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="126" spans="2:36">
-      <c r="B126" s="158"/>
-      <c r="D126" s="154"/>
+    <row r="126" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B126" s="164"/>
+      <c r="D126" s="160"/>
       <c r="E126" s="79" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="F126" s="80" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G126" s="86">
         <f t="shared" ref="G126:G127" si="11">10/24</f>
@@ -15352,14 +15350,14 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="127" spans="2:36">
-      <c r="B127" s="158"/>
-      <c r="D127" s="154"/>
+    <row r="127" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B127" s="164"/>
+      <c r="D127" s="160"/>
       <c r="E127" s="79" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="F127" s="80" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G127" s="86">
         <f t="shared" si="11"/>
@@ -15453,27 +15451,27 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="128" spans="2:36">
+    <row r="128" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B128" s="87"/>
     </row>
-    <row r="129" spans="2:28">
-      <c r="B129" s="156" t="s">
-        <v>91</v>
-      </c>
-      <c r="C129" s="155"/>
-      <c r="D129" s="155"/>
-      <c r="E129" s="155"/>
-      <c r="F129" s="155"/>
-      <c r="G129" s="155"/>
-      <c r="H129" s="155"/>
-      <c r="I129" s="155"/>
-      <c r="J129" s="155"/>
-      <c r="K129" s="155"/>
-      <c r="L129" s="155"/>
-      <c r="M129" s="155"/>
-      <c r="N129" s="155"/>
-      <c r="O129" s="155"/>
-      <c r="P129" s="155"/>
+    <row r="129" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B129" s="162" t="s">
+        <v>111</v>
+      </c>
+      <c r="C129" s="161"/>
+      <c r="D129" s="161"/>
+      <c r="E129" s="161"/>
+      <c r="F129" s="161"/>
+      <c r="G129" s="161"/>
+      <c r="H129" s="161"/>
+      <c r="I129" s="161"/>
+      <c r="J129" s="161"/>
+      <c r="K129" s="161"/>
+      <c r="L129" s="161"/>
+      <c r="M129" s="161"/>
+      <c r="N129" s="161"/>
+      <c r="O129" s="161"/>
+      <c r="P129" s="161"/>
       <c r="Q129" s="50"/>
       <c r="R129" s="50"/>
       <c r="S129" s="50"/>
@@ -15482,7 +15480,7 @@
       <c r="V129" s="50"/>
       <c r="W129" s="50"/>
     </row>
-    <row r="130" spans="2:28" ht="15.75" thickBot="1">
+    <row r="130" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B130" s="40"/>
       <c r="C130" s="40"/>
       <c r="D130" s="40"/>
@@ -15506,28 +15504,28 @@
       <c r="V130" s="40"/>
       <c r="W130" s="40"/>
     </row>
-    <row r="131" spans="2:28">
+    <row r="131" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B131" s="40"/>
-      <c r="C131" s="146" t="s">
-        <v>92</v>
-      </c>
-      <c r="D131" s="147"/>
-      <c r="E131" s="147"/>
-      <c r="F131" s="147"/>
-      <c r="G131" s="147"/>
-      <c r="H131" s="147"/>
-      <c r="I131" s="149" t="s">
-        <v>93</v>
-      </c>
-      <c r="J131" s="150"/>
-      <c r="K131" s="150"/>
-      <c r="L131" s="150"/>
-      <c r="M131" s="151"/>
+      <c r="C131" s="152" t="s">
+        <v>112</v>
+      </c>
+      <c r="D131" s="153"/>
+      <c r="E131" s="153"/>
+      <c r="F131" s="153"/>
+      <c r="G131" s="153"/>
+      <c r="H131" s="153"/>
+      <c r="I131" s="155" t="s">
+        <v>113</v>
+      </c>
+      <c r="J131" s="156"/>
+      <c r="K131" s="156"/>
+      <c r="L131" s="156"/>
+      <c r="M131" s="157"/>
       <c r="N131" s="89" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="O131" s="90" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="P131" s="91"/>
       <c r="Q131" s="91"/>
@@ -15538,36 +15536,36 @@
       <c r="V131" s="91"/>
       <c r="W131" s="92"/>
     </row>
-    <row r="132" spans="2:28" ht="14.85" customHeight="1">
+    <row r="132" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="40"/>
-      <c r="C132" s="181" t="s">
-        <v>96</v>
-      </c>
-      <c r="D132" s="182"/>
-      <c r="E132" s="182"/>
-      <c r="F132" s="182"/>
-      <c r="G132" s="182"/>
-      <c r="H132" s="183"/>
+      <c r="C132" s="142" t="s">
+        <v>116</v>
+      </c>
+      <c r="D132" s="143"/>
+      <c r="E132" s="143"/>
+      <c r="F132" s="143"/>
+      <c r="G132" s="143"/>
+      <c r="H132" s="144"/>
       <c r="I132" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="M132" s="96"/>
       <c r="N132" s="97"/>
       <c r="O132" s="98"/>
       <c r="W132" s="99"/>
     </row>
-    <row r="133" spans="2:28" ht="14.85" customHeight="1">
+    <row r="133" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="40"/>
-      <c r="C133" s="181" t="s">
-        <v>97</v>
-      </c>
-      <c r="D133" s="182"/>
-      <c r="E133" s="182"/>
-      <c r="F133" s="182"/>
-      <c r="G133" s="182"/>
-      <c r="H133" s="183"/>
+      <c r="C133" s="142" t="s">
+        <v>117</v>
+      </c>
+      <c r="D133" s="143"/>
+      <c r="E133" s="143"/>
+      <c r="F133" s="143"/>
+      <c r="G133" s="143"/>
+      <c r="H133" s="144"/>
       <c r="I133" s="100" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="J133" s="101"/>
       <c r="K133" s="101"/>
@@ -15576,7 +15574,7 @@
       <c r="N133" s="103"/>
       <c r="O133" s="103"/>
       <c r="P133" s="101" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="Q133" s="101"/>
       <c r="R133" s="101"/>
@@ -15586,23 +15584,23 @@
       <c r="V133" s="101"/>
       <c r="W133" s="104"/>
     </row>
-    <row r="134" spans="2:28" ht="45" customHeight="1">
+    <row r="134" spans="2:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B134" s="40"/>
-      <c r="C134" s="181" t="s">
-        <v>86</v>
-      </c>
-      <c r="D134" s="182"/>
-      <c r="E134" s="182"/>
-      <c r="F134" s="182"/>
-      <c r="G134" s="182"/>
-      <c r="H134" s="183"/>
-      <c r="I134" s="142" t="s">
-        <v>99</v>
-      </c>
-      <c r="J134" s="143"/>
-      <c r="K134" s="143"/>
-      <c r="L134" s="143"/>
-      <c r="M134" s="144"/>
+      <c r="C134" s="142" t="s">
+        <v>106</v>
+      </c>
+      <c r="D134" s="143"/>
+      <c r="E134" s="143"/>
+      <c r="F134" s="143"/>
+      <c r="G134" s="143"/>
+      <c r="H134" s="144"/>
+      <c r="I134" s="148" t="s">
+        <v>119</v>
+      </c>
+      <c r="J134" s="149"/>
+      <c r="K134" s="149"/>
+      <c r="L134" s="149"/>
+      <c r="M134" s="150"/>
       <c r="N134" s="105"/>
       <c r="O134" s="105"/>
       <c r="P134" s="106"/>
@@ -15614,23 +15612,23 @@
       <c r="V134" s="106"/>
       <c r="W134" s="107"/>
     </row>
-    <row r="135" spans="2:28" ht="46.5" customHeight="1">
+    <row r="135" spans="2:28" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="40"/>
-      <c r="C135" s="181" t="s">
-        <v>100</v>
-      </c>
-      <c r="D135" s="182"/>
-      <c r="E135" s="182"/>
-      <c r="F135" s="182"/>
-      <c r="G135" s="182"/>
-      <c r="H135" s="183"/>
-      <c r="I135" s="142" t="s">
-        <v>101</v>
-      </c>
-      <c r="J135" s="143"/>
-      <c r="K135" s="143"/>
-      <c r="L135" s="143"/>
-      <c r="M135" s="144"/>
+      <c r="C135" s="142" t="s">
+        <v>120</v>
+      </c>
+      <c r="D135" s="143"/>
+      <c r="E135" s="143"/>
+      <c r="F135" s="143"/>
+      <c r="G135" s="143"/>
+      <c r="H135" s="144"/>
+      <c r="I135" s="148" t="s">
+        <v>121</v>
+      </c>
+      <c r="J135" s="149"/>
+      <c r="K135" s="149"/>
+      <c r="L135" s="149"/>
+      <c r="M135" s="150"/>
       <c r="N135" s="105"/>
       <c r="O135" s="105"/>
       <c r="P135" s="106"/>
@@ -15642,18 +15640,18 @@
       <c r="V135" s="106"/>
       <c r="W135" s="107"/>
     </row>
-    <row r="136" spans="2:28">
+    <row r="136" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B136" s="40"/>
-      <c r="C136" s="181" t="s">
-        <v>102</v>
-      </c>
-      <c r="D136" s="182"/>
-      <c r="E136" s="182"/>
-      <c r="F136" s="182"/>
-      <c r="G136" s="182"/>
-      <c r="H136" s="183"/>
+      <c r="C136" s="142" t="s">
+        <v>122</v>
+      </c>
+      <c r="D136" s="143"/>
+      <c r="E136" s="143"/>
+      <c r="F136" s="143"/>
+      <c r="G136" s="143"/>
+      <c r="H136" s="144"/>
       <c r="I136" s="108" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="J136" s="109"/>
       <c r="K136" s="109"/>
@@ -15670,18 +15668,18 @@
       <c r="V136" s="109"/>
       <c r="W136" s="111"/>
     </row>
-    <row r="137" spans="2:28" ht="15.75" thickBot="1">
+    <row r="137" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B137" s="40"/>
-      <c r="C137" s="184" t="s">
-        <v>103</v>
-      </c>
-      <c r="D137" s="185"/>
-      <c r="E137" s="185"/>
-      <c r="F137" s="185"/>
-      <c r="G137" s="185"/>
-      <c r="H137" s="186"/>
+      <c r="C137" s="145" t="s">
+        <v>123</v>
+      </c>
+      <c r="D137" s="146"/>
+      <c r="E137" s="146"/>
+      <c r="F137" s="146"/>
+      <c r="G137" s="146"/>
+      <c r="H137" s="147"/>
       <c r="I137" s="112" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="J137" s="113"/>
       <c r="K137" s="113"/>
@@ -15698,14 +15696,14 @@
       <c r="V137" s="113"/>
       <c r="W137" s="115"/>
     </row>
-    <row r="138" spans="2:28" ht="15.75" thickBot="1">
+    <row r="138" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B138" s="40"/>
-      <c r="C138" s="145"/>
-      <c r="D138" s="145"/>
-      <c r="E138" s="145"/>
-      <c r="F138" s="145"/>
-      <c r="G138" s="145"/>
-      <c r="H138" s="145"/>
+      <c r="C138" s="151"/>
+      <c r="D138" s="151"/>
+      <c r="E138" s="151"/>
+      <c r="F138" s="151"/>
+      <c r="G138" s="151"/>
+      <c r="H138" s="151"/>
       <c r="I138" s="116"/>
       <c r="J138" s="116"/>
       <c r="K138" s="116"/>
@@ -15722,28 +15720,28 @@
       <c r="V138" s="117"/>
       <c r="W138" s="117"/>
     </row>
-    <row r="139" spans="2:28">
+    <row r="139" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B139" s="40"/>
-      <c r="C139" s="146" t="s">
-        <v>104</v>
-      </c>
-      <c r="D139" s="147"/>
-      <c r="E139" s="147"/>
-      <c r="F139" s="147"/>
-      <c r="G139" s="147"/>
-      <c r="H139" s="148"/>
-      <c r="I139" s="149" t="s">
-        <v>93</v>
-      </c>
-      <c r="J139" s="150"/>
-      <c r="K139" s="150"/>
-      <c r="L139" s="150"/>
-      <c r="M139" s="151"/>
+      <c r="C139" s="152" t="s">
+        <v>124</v>
+      </c>
+      <c r="D139" s="153"/>
+      <c r="E139" s="153"/>
+      <c r="F139" s="153"/>
+      <c r="G139" s="153"/>
+      <c r="H139" s="154"/>
+      <c r="I139" s="155" t="s">
+        <v>113</v>
+      </c>
+      <c r="J139" s="156"/>
+      <c r="K139" s="156"/>
+      <c r="L139" s="156"/>
+      <c r="M139" s="157"/>
       <c r="N139" s="89" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="O139" s="89" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="P139" s="118"/>
       <c r="Q139" s="119"/>
@@ -15754,18 +15752,18 @@
       <c r="V139" s="119"/>
       <c r="W139" s="120"/>
     </row>
-    <row r="140" spans="2:28">
+    <row r="140" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B140" s="40"/>
-      <c r="C140" s="181" t="s">
-        <v>97</v>
-      </c>
-      <c r="D140" s="182"/>
-      <c r="E140" s="182"/>
-      <c r="F140" s="182"/>
-      <c r="G140" s="182"/>
-      <c r="H140" s="183"/>
+      <c r="C140" s="142" t="s">
+        <v>117</v>
+      </c>
+      <c r="D140" s="143"/>
+      <c r="E140" s="143"/>
+      <c r="F140" s="143"/>
+      <c r="G140" s="143"/>
+      <c r="H140" s="144"/>
       <c r="I140" s="100" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="J140" s="101"/>
       <c r="K140" s="101"/>
@@ -15774,7 +15772,7 @@
       <c r="N140" s="103"/>
       <c r="O140" s="103"/>
       <c r="P140" s="101" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="Q140" s="101"/>
       <c r="R140" s="101"/>
@@ -15784,10 +15782,10 @@
       <c r="V140" s="101"/>
       <c r="W140" s="104"/>
     </row>
-    <row r="141" spans="2:28">
+    <row r="141" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B141" s="40"/>
       <c r="C141" s="93" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D141" s="94"/>
       <c r="E141" s="94"/>
@@ -15795,7 +15793,7 @@
       <c r="G141" s="94"/>
       <c r="H141" s="95"/>
       <c r="I141" s="122" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="J141" s="123"/>
       <c r="K141" s="123"/>
@@ -15812,9 +15810,9 @@
       <c r="V141" s="123"/>
       <c r="W141" s="126"/>
     </row>
-    <row r="142" spans="2:28" s="40" customFormat="1" ht="14.25" customHeight="1">
+    <row r="142" spans="2:28" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C142" s="93" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="D142" s="94"/>
       <c r="E142" s="94"/>
@@ -15822,7 +15820,7 @@
       <c r="G142" s="94"/>
       <c r="H142" s="95"/>
       <c r="I142" s="127" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="J142" s="127"/>
       <c r="K142" s="127"/>
@@ -15830,7 +15828,7 @@
       <c r="M142" s="127"/>
       <c r="O142" s="128"/>
       <c r="P142" s="129" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="Q142" s="94"/>
       <c r="R142" s="95"/>
@@ -15845,18 +15843,18 @@
       <c r="AA142" s="94"/>
       <c r="AB142" s="95"/>
     </row>
-    <row r="143" spans="2:28">
+    <row r="143" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B143" s="40"/>
-      <c r="C143" s="181" t="s">
-        <v>100</v>
-      </c>
-      <c r="D143" s="182"/>
-      <c r="E143" s="182"/>
-      <c r="F143" s="182"/>
-      <c r="G143" s="182"/>
-      <c r="H143" s="183"/>
+      <c r="C143" s="142" t="s">
+        <v>120</v>
+      </c>
+      <c r="D143" s="143"/>
+      <c r="E143" s="143"/>
+      <c r="F143" s="143"/>
+      <c r="G143" s="143"/>
+      <c r="H143" s="144"/>
       <c r="I143" s="122" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="J143" s="131"/>
       <c r="K143" s="131"/>
@@ -15873,18 +15871,18 @@
       <c r="V143" s="131"/>
       <c r="W143" s="134"/>
     </row>
-    <row r="144" spans="2:28">
+    <row r="144" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B144" s="40"/>
-      <c r="C144" s="181" t="s">
-        <v>102</v>
-      </c>
-      <c r="D144" s="182"/>
-      <c r="E144" s="182"/>
-      <c r="F144" s="182"/>
-      <c r="G144" s="182"/>
-      <c r="H144" s="183"/>
+      <c r="C144" s="142" t="s">
+        <v>122</v>
+      </c>
+      <c r="D144" s="143"/>
+      <c r="E144" s="143"/>
+      <c r="F144" s="143"/>
+      <c r="G144" s="143"/>
+      <c r="H144" s="144"/>
       <c r="I144" s="122" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="J144" s="109"/>
       <c r="K144" s="109"/>
@@ -15901,18 +15899,18 @@
       <c r="V144" s="109"/>
       <c r="W144" s="111"/>
     </row>
-    <row r="145" spans="2:23" ht="15.75" thickBot="1">
+    <row r="145" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B145" s="40"/>
-      <c r="C145" s="184" t="s">
-        <v>108</v>
-      </c>
-      <c r="D145" s="185"/>
-      <c r="E145" s="185"/>
-      <c r="F145" s="185"/>
-      <c r="G145" s="185"/>
-      <c r="H145" s="186"/>
+      <c r="C145" s="145" t="s">
+        <v>128</v>
+      </c>
+      <c r="D145" s="146"/>
+      <c r="E145" s="146"/>
+      <c r="F145" s="146"/>
+      <c r="G145" s="146"/>
+      <c r="H145" s="147"/>
       <c r="I145" s="112" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="J145" s="113"/>
       <c r="K145" s="113"/>
@@ -15929,235 +15927,235 @@
       <c r="V145" s="113"/>
       <c r="W145" s="115"/>
     </row>
-    <row r="146" spans="2:23">
+    <row r="146" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B146" s="87"/>
     </row>
-    <row r="147" spans="2:23">
+    <row r="147" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B147" s="87"/>
     </row>
-    <row r="148" spans="2:23">
+    <row r="148" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B148" s="87"/>
     </row>
-    <row r="149" spans="2:23">
+    <row r="149" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B149" s="87"/>
     </row>
-    <row r="150" spans="2:23">
+    <row r="150" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B150" s="87"/>
     </row>
-    <row r="151" spans="2:23">
+    <row r="151" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B151" s="87"/>
     </row>
-    <row r="152" spans="2:23">
+    <row r="152" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B152" s="87"/>
     </row>
-    <row r="153" spans="2:23">
+    <row r="153" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B153" s="87"/>
     </row>
-    <row r="154" spans="2:23">
+    <row r="154" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B154" s="87"/>
     </row>
-    <row r="155" spans="2:23">
+    <row r="155" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B155" s="87"/>
     </row>
-    <row r="156" spans="2:23">
+    <row r="156" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B156" s="87"/>
     </row>
-    <row r="157" spans="2:23">
+    <row r="157" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B157" s="87"/>
     </row>
-    <row r="158" spans="2:23">
+    <row r="158" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B158" s="87"/>
     </row>
-    <row r="159" spans="2:23">
+    <row r="159" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B159" s="87"/>
     </row>
-    <row r="160" spans="2:23">
+    <row r="160" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B160" s="87"/>
     </row>
-    <row r="161" spans="2:2">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B161" s="87"/>
     </row>
-    <row r="162" spans="2:2">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B162" s="87"/>
     </row>
-    <row r="163" spans="2:2">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B163" s="87"/>
     </row>
-    <row r="164" spans="2:2">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B164" s="87"/>
     </row>
-    <row r="165" spans="2:2">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B165" s="87"/>
     </row>
-    <row r="166" spans="2:2">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B166" s="87"/>
     </row>
-    <row r="167" spans="2:2">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B167" s="87"/>
     </row>
-    <row r="168" spans="2:2">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B168" s="87"/>
     </row>
-    <row r="169" spans="2:2">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B169" s="87"/>
     </row>
-    <row r="170" spans="2:2">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B170" s="87"/>
     </row>
-    <row r="171" spans="2:2">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B171" s="87"/>
     </row>
-    <row r="172" spans="2:2">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B172" s="87"/>
     </row>
-    <row r="173" spans="2:2">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B173" s="87"/>
     </row>
-    <row r="174" spans="2:2">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B174" s="87"/>
     </row>
-    <row r="175" spans="2:2">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B175" s="87"/>
     </row>
-    <row r="176" spans="2:2">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B176" s="87"/>
     </row>
-    <row r="177" spans="2:2">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B177" s="87"/>
     </row>
-    <row r="178" spans="2:2">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B178" s="87"/>
     </row>
-    <row r="179" spans="2:2">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B179" s="87"/>
     </row>
-    <row r="180" spans="2:2">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B180" s="87"/>
     </row>
-    <row r="181" spans="2:2">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B181" s="87"/>
     </row>
-    <row r="182" spans="2:2">
+    <row r="182" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B182" s="87"/>
     </row>
-    <row r="183" spans="2:2">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B183" s="87"/>
     </row>
-    <row r="184" spans="2:2">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B184" s="87"/>
     </row>
-    <row r="185" spans="2:2">
+    <row r="185" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B185" s="87"/>
     </row>
-    <row r="186" spans="2:2">
+    <row r="186" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B186" s="87"/>
     </row>
-    <row r="187" spans="2:2">
+    <row r="187" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B187" s="87"/>
     </row>
-    <row r="188" spans="2:2">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B188" s="87"/>
     </row>
-    <row r="189" spans="2:2">
+    <row r="189" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B189" s="87"/>
     </row>
-    <row r="190" spans="2:2">
+    <row r="190" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B190" s="87"/>
     </row>
-    <row r="191" spans="2:2">
+    <row r="191" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B191" s="87"/>
     </row>
-    <row r="192" spans="2:2">
+    <row r="192" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B192" s="87"/>
     </row>
-    <row r="193" spans="2:2">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B193" s="87"/>
     </row>
-    <row r="194" spans="2:2">
+    <row r="194" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B194" s="87"/>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B195" s="87"/>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B196" s="87"/>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B197" s="87"/>
     </row>
-    <row r="198" spans="2:2">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B198" s="87"/>
     </row>
-    <row r="199" spans="2:2">
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B199" s="87"/>
     </row>
-    <row r="200" spans="2:2">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B200" s="87"/>
     </row>
-    <row r="201" spans="2:2">
+    <row r="201" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B201" s="87"/>
     </row>
-    <row r="202" spans="2:2">
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B202" s="87"/>
     </row>
-    <row r="203" spans="2:2">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B203" s="87"/>
     </row>
-    <row r="204" spans="2:2">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B204" s="87"/>
     </row>
-    <row r="205" spans="2:2">
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B205" s="87"/>
     </row>
-    <row r="206" spans="2:2">
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B206" s="87"/>
     </row>
-    <row r="207" spans="2:2">
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B207" s="87"/>
     </row>
-    <row r="208" spans="2:2">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B208" s="87"/>
     </row>
-    <row r="209" spans="2:2">
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B209" s="87"/>
     </row>
-    <row r="210" spans="2:2">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B210" s="87"/>
     </row>
-    <row r="211" spans="2:2">
+    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B211" s="87"/>
     </row>
-    <row r="212" spans="2:2">
+    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B212" s="87"/>
     </row>
-    <row r="213" spans="2:2">
+    <row r="213" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B213" s="87"/>
     </row>
-    <row r="214" spans="2:2">
+    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B214" s="87"/>
     </row>
-    <row r="215" spans="2:2">
+    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B215" s="87"/>
     </row>
-    <row r="216" spans="2:2">
+    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B216" s="87"/>
     </row>
-    <row r="217" spans="2:2">
+    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B217" s="87"/>
     </row>
-    <row r="218" spans="2:2">
+    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B218" s="87"/>
     </row>
-    <row r="219" spans="2:2">
+    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B219" s="87"/>
     </row>
-    <row r="220" spans="2:2">
+    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B220" s="87"/>
     </row>
-    <row r="221" spans="2:2">
+    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B221" s="87"/>
     </row>
-    <row r="222" spans="2:2">
+    <row r="222" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B222" s="87"/>
     </row>
   </sheetData>
@@ -16215,15 +16213,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC34B27C-0BFA-4D35-874E-EA84BA74EBE0}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.5703125" customWidth="1"/>
     <col min="2" max="14" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -16239,75 +16237,75 @@
       <c r="M1" s="33"/>
       <c r="N1" s="33"/>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
-      <c r="B2" s="176" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" s="177"/>
-      <c r="D2" s="178"/>
+      <c r="B2" s="184" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="185"/>
+      <c r="D2" s="186"/>
       <c r="E2" s="39"/>
-      <c r="F2" s="176" t="s">
-        <v>111</v>
-      </c>
-      <c r="G2" s="177"/>
-      <c r="H2" s="178"/>
-      <c r="I2" s="176" t="s">
-        <v>112</v>
-      </c>
-      <c r="J2" s="177"/>
-      <c r="K2" s="178"/>
-      <c r="L2" s="176" t="s">
-        <v>113</v>
-      </c>
-      <c r="M2" s="177"/>
-      <c r="N2" s="178"/>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="F2" s="184" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="185"/>
+      <c r="H2" s="186"/>
+      <c r="I2" s="184" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="185"/>
+      <c r="K2" s="186"/>
+      <c r="L2" s="184" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="185"/>
+      <c r="N2" s="186"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="E3" s="20"/>
       <c r="F3" s="21" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="J3" s="20" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="M3" s="20" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="B4" s="9">
         <v>50160000</v>
@@ -16350,9 +16348,9 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="B5" s="9">
         <v>4200000</v>
@@ -16395,9 +16393,9 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="B6" s="9">
         <v>3121131</v>
@@ -16440,9 +16438,9 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="B7" s="9">
         <v>8602825</v>
@@ -16485,9 +16483,9 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="B8" s="9">
         <v>5479149</v>
@@ -16530,9 +16528,9 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="B9" s="9">
         <v>2775545</v>
@@ -16575,9 +16573,9 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="B10" s="9">
         <v>5293460</v>
@@ -16620,9 +16618,9 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="B11" s="23">
         <v>79632110</v>
@@ -16665,9 +16663,9 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="B12" s="7">
         <v>250000</v>
@@ -16707,9 +16705,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="B13" s="9">
         <v>295289</v>
@@ -16749,9 +16747,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="B14" s="9">
         <v>1802363</v>
@@ -16791,9 +16789,9 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="B15" s="9">
         <v>2477135</v>
@@ -16833,9 +16831,9 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="B16" s="9">
         <v>2477135</v>
@@ -16875,9 +16873,9 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="B17" s="9">
         <v>4346702</v>
@@ -16917,9 +16915,9 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="B18" s="28">
         <v>11648623</v>
@@ -16959,14 +16957,14 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="D22" s="35">
         <f>SUM(D5:D9,D12:D17)</f>
@@ -16974,12 +16972,12 @@
       </c>
       <c r="E22" s="35"/>
       <c r="F22" s="37" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="D23" s="36">
         <f>D10*SUM(D5:D7)/SUM(D4:D7)</f>
@@ -16987,12 +16985,12 @@
       </c>
       <c r="E23" s="36"/>
       <c r="F23" s="37" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D24" s="35">
         <f>SUM(D22:D23)</f>
@@ -17000,12 +16998,12 @@
       </c>
       <c r="E24" s="35"/>
       <c r="F24" s="37" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D25" s="5">
         <f>D24*10^6</f>
@@ -17013,12 +17011,12 @@
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D26" s="5">
         <f>D25*About!A48</f>
@@ -17026,12 +17024,12 @@
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -17049,14 +17047,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD9A83FF-6D12-451D-B709-5F68973469C6}">
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -17149,9 +17147,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B2">
         <v>272875</v>
@@ -17163,94 +17161,94 @@
         <v>303546</v>
       </c>
       <c r="E2">
-        <v>277345</v>
+        <v>274986</v>
       </c>
       <c r="F2">
-        <v>256728</v>
+        <v>253296</v>
       </c>
       <c r="G2">
-        <v>240275</v>
+        <v>236734</v>
       </c>
       <c r="H2">
-        <v>226464</v>
+        <v>223030</v>
       </c>
       <c r="I2">
-        <v>214618</v>
+        <v>211554</v>
       </c>
       <c r="J2">
-        <v>204553</v>
+        <v>201954</v>
       </c>
       <c r="K2">
-        <v>196075</v>
+        <v>193764</v>
       </c>
       <c r="L2">
-        <v>188655</v>
+        <v>186541</v>
       </c>
       <c r="M2">
-        <v>182183</v>
+        <v>180196</v>
       </c>
       <c r="N2">
-        <v>176401</v>
+        <v>174552</v>
       </c>
       <c r="O2">
-        <v>171611</v>
+        <v>169876</v>
       </c>
       <c r="P2">
-        <v>167430</v>
+        <v>165776</v>
       </c>
       <c r="Q2">
-        <v>163809</v>
+        <v>162216</v>
       </c>
       <c r="R2">
-        <v>160633</v>
+        <v>159077</v>
       </c>
       <c r="S2">
-        <v>157780</v>
+        <v>156257</v>
       </c>
       <c r="T2">
-        <v>155218</v>
+        <v>153722</v>
       </c>
       <c r="U2">
-        <v>152921</v>
+        <v>151442</v>
       </c>
       <c r="V2">
-        <v>150890</v>
+        <v>149428</v>
       </c>
       <c r="W2">
-        <v>149018</v>
+        <v>147587</v>
       </c>
       <c r="X2">
-        <v>147310</v>
+        <v>145898</v>
       </c>
       <c r="Y2">
-        <v>145744</v>
+        <v>144352</v>
       </c>
       <c r="Z2">
-        <v>144287</v>
+        <v>142921</v>
       </c>
       <c r="AA2">
-        <v>142963</v>
+        <v>141617</v>
       </c>
       <c r="AB2">
-        <v>141726</v>
+        <v>140396</v>
       </c>
       <c r="AC2">
-        <v>140576</v>
+        <v>139257</v>
       </c>
       <c r="AD2">
-        <v>139495</v>
+        <v>138188</v>
       </c>
       <c r="AE2">
-        <v>138485</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31">
+        <v>137190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="C3">
-        <f t="shared" ref="C3:AE3" si="0">C9*$B$12*1000</f>
+        <f>C9*$B$12*1000</f>
         <v>306878.94936720002</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D3:AE3" si="0">D9*$B$12*1000</f>
         <v>303731.66899460001</v>
       </c>
       <c r="E3">
@@ -17362,9 +17360,9 @@
         <v>123431.08661402132</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B5">
         <v>2021</v>
@@ -17457,9 +17455,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B6">
         <v>253384</v>
@@ -17552,7 +17550,7 @@
         <v>212064</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="C7">
         <f t="shared" ref="C7:AE7" si="1">C10*$B$12*1000</f>
         <v>284959.40253119997</v>
@@ -17670,12 +17668,12 @@
         <v>212193.12422562522</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C9">
         <v>390.92859792000002</v>
@@ -17765,12 +17763,12 @@
         <v>157.23705301149212</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C10">
         <v>363.00560831999996</v>
@@ -17860,9 +17858,9 @@
         <v>270.30971238933148</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B12">
         <v>0.78500000000000003</v>
@@ -17879,58 +17877,62 @@
   <sheetPr>
     <tabColor rgb="FF003399"/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2021</v>
       </c>
       <c r="B2" s="5">
-        <v>0</v>
+        <f>'NREL ATB 2024'!F20*1000*About!A51</f>
+        <v>272875.18454364559</v>
       </c>
       <c r="E2" s="5"/>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2022</v>
       </c>
       <c r="B3" s="5">
-        <v>0</v>
+        <f>'NREL ATB 2024'!G20*1000*cpi_2022_to_2012</f>
+        <v>306691.70357876847</v>
       </c>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2023</v>
       </c>
       <c r="B4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <f>'NREL ATB 2024'!H20*1000*cpi_2022_to_2012</f>
+        <v>303546.34355618269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2024</v>
       </c>
       <c r="B5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <f>'NREL ATB 2024'!I20*1000*cpi_2022_to_2012</f>
+        <v>279096.37947464635</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -17938,7 +17940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2026</v>
       </c>
@@ -17946,7 +17948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2027</v>
       </c>
@@ -17954,7 +17956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2028</v>
       </c>
@@ -17962,7 +17964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2029</v>
       </c>
@@ -17970,7 +17972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2030</v>
       </c>
@@ -17978,7 +17980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2031</v>
       </c>
@@ -17986,7 +17988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2032</v>
       </c>
@@ -17994,7 +17996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2033</v>
       </c>
@@ -18002,7 +18004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2034</v>
       </c>
@@ -18010,7 +18012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2035</v>
       </c>
@@ -18018,7 +18020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2036</v>
       </c>
@@ -18026,7 +18028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2037</v>
       </c>
@@ -18034,7 +18036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2038</v>
       </c>
@@ -18042,7 +18044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2039</v>
       </c>
@@ -18050,7 +18052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2040</v>
       </c>
@@ -18058,7 +18060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2041</v>
       </c>
@@ -18066,7 +18068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2042</v>
       </c>
@@ -18074,7 +18076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2043</v>
       </c>
@@ -18082,7 +18084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2044</v>
       </c>
@@ -18090,7 +18092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2045</v>
       </c>
@@ -18098,7 +18100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2046</v>
       </c>
@@ -18106,7 +18108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2047</v>
       </c>
@@ -18114,7 +18116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2048</v>
       </c>
@@ -18122,7 +18124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2049</v>
       </c>
@@ -18130,7 +18132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2050</v>
       </c>
@@ -18138,7 +18140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2051</v>
       </c>
@@ -18146,7 +18148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2052</v>
       </c>
@@ -18154,7 +18156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2053</v>
       </c>
@@ -18162,7 +18164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2054</v>
       </c>
@@ -18170,7 +18172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2055</v>
       </c>
@@ -18178,7 +18180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2056</v>
       </c>
@@ -18186,7 +18188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2057</v>
       </c>
@@ -18194,7 +18196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2058</v>
       </c>
@@ -18202,7 +18204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2059</v>
       </c>
@@ -18210,7 +18212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2060</v>
       </c>
@@ -18218,7 +18220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2061</v>
       </c>
@@ -18226,7 +18228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2062</v>
       </c>
@@ -18234,7 +18236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2063</v>
       </c>
@@ -18242,7 +18244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2064</v>
       </c>
@@ -18250,7 +18252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2065</v>
       </c>
@@ -18258,7 +18260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2066</v>
       </c>
@@ -18266,7 +18268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2067</v>
       </c>
@@ -18274,7 +18276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2068</v>
       </c>
@@ -18282,7 +18284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2069</v>
       </c>
@@ -18290,13 +18292,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2070</v>
       </c>
       <c r="B51" s="5">
         <v>0</v>
       </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="5"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18309,22 +18317,22 @@
     <tabColor rgb="FF003399"/>
   </sheetPr>
   <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2021</v>
       </c>
@@ -18334,7 +18342,7 @@
       </c>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2022</v>
       </c>
@@ -18343,7 +18351,7 @@
         <v>284785.53121122846</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -18352,7 +18360,7 @@
         <v>281864.83588615071</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2024</v>
       </c>
@@ -18361,7 +18369,7 @@
         <v>272119.91517411894</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -18370,7 +18378,7 @@
         <v>244267.93200601047</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2026</v>
       </c>
@@ -18379,7 +18387,7 @@
         <v>245045.09148289612</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2027</v>
       </c>
@@ -18388,7 +18396,7 @@
         <v>245896.5501406297</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2028</v>
       </c>
@@ -18397,7 +18405,7 @@
         <v>246831.28958028281</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2029</v>
       </c>
@@ -18406,7 +18414,7 @@
         <v>247859.79983015926</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2030</v>
       </c>
@@ -18415,7 +18423,7 @@
         <v>248994.40989292334</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2031</v>
       </c>
@@ -18424,7 +18432,7 @@
         <v>247303.59777741029</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2032</v>
       </c>
@@ -18433,7 +18441,7 @@
         <v>245600.17607833183</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2033</v>
       </c>
@@ -18442,7 +18450,7 @@
         <v>243883.65354072856</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2034</v>
       </c>
@@ -18451,7 +18459,7 @@
         <v>242153.5130555816</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2035</v>
       </c>
@@ -18460,7 +18468,7 @@
         <v>240409.20993631281</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2036</v>
       </c>
@@ -18469,7 +18477,7 @@
         <v>238650.17005554074</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2037</v>
       </c>
@@ -18478,7 +18486,7 @@
         <v>236875.78782870833</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2038</v>
       </c>
@@ -18487,7 +18495,7 @@
         <v>235085.42402968768</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2039</v>
       </c>
@@ -18496,7 +18504,7 @@
         <v>233278.40342179779</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2040</v>
       </c>
@@ -18505,7 +18513,7 @@
         <v>231454.01218578266</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2041</v>
       </c>
@@ -18514,7 +18522,7 @@
         <v>229611.49512414529</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2042</v>
       </c>
@@ -18523,7 +18531,7 @@
         <v>227750.05261882479</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2043</v>
       </c>
@@ -18532,7 +18540,7 @@
         <v>225868.83731644039</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2044</v>
       </c>
@@ -18541,7 +18549,7 @@
         <v>223966.95051221756</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2045</v>
       </c>
@@ -18550,7 +18558,7 @@
         <v>222043.43820014191</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2046</v>
       </c>
@@ -18559,7 +18567,7 @@
         <v>220097.2867528405</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2047</v>
       </c>
@@ -18568,7 +18576,7 @@
         <v>218127.41819005259</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2048</v>
       </c>
@@ -18577,7 +18585,7 @@
         <v>216132.68498924136</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2049</v>
       </c>
@@ -18586,7 +18594,7 @@
         <v>214111.864385811</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2050</v>
       </c>
@@ -18595,184 +18603,184 @@
         <v>212063.65210338513</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2051</v>
       </c>
       <c r="B32" s="5">
-        <f>B31</f>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <f>_xlfn.FORECAST.LINEAR(A32,$B$21:$B$31,$A$21:$A$31)</f>
+        <v>210303.15776537685</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2052</v>
       </c>
       <c r="B33" s="5">
-        <f t="shared" ref="B33:B51" si="0">B32</f>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <f t="shared" ref="B33:B51" si="0">_xlfn.FORECAST.LINEAR(A33,$B$21:$B$31,$A$21:$A$31)</f>
+        <v>208365.38569022948</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2053</v>
       </c>
       <c r="B34" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>206427.61361508165</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2054</v>
       </c>
       <c r="B35" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>204489.84153993428</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2055</v>
       </c>
       <c r="B36" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>202552.06946478691</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2056</v>
       </c>
       <c r="B37" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>200614.29738963908</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2057</v>
       </c>
       <c r="B38" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>198676.52531449171</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2058</v>
       </c>
       <c r="B39" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>196738.75323934434</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2059</v>
       </c>
       <c r="B40" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>194800.98116419651</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2060</v>
       </c>
       <c r="B41" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>192863.20908904914</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2061</v>
       </c>
       <c r="B42" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>190925.43701390177</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2062</v>
       </c>
       <c r="B43" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>188987.66493875394</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2063</v>
       </c>
       <c r="B44" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>187049.89286360657</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2064</v>
       </c>
       <c r="B45" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>185112.1207884592</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2065</v>
       </c>
       <c r="B46" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>183174.34871331137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2066</v>
       </c>
       <c r="B47" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>181236.576638164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2067</v>
       </c>
       <c r="B48" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>179298.80456301663</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2068</v>
       </c>
       <c r="B49" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>177361.0324878688</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2069</v>
       </c>
       <c r="B50" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>175423.26041272143</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2070</v>
       </c>
       <c r="B51" s="5">
         <f t="shared" si="0"/>
-        <v>212063.65210338513</v>
+        <v>173485.48833757406</v>
       </c>
     </row>
   </sheetData>
@@ -18785,229 +18793,305 @@
   <sheetPr>
     <tabColor rgb="FF003399"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:AV2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31">
+        <v>130</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+      <c r="AC1">
+        <v>2051</v>
+      </c>
+      <c r="AD1">
+        <v>2052</v>
+      </c>
+      <c r="AE1">
+        <v>2053</v>
+      </c>
+      <c r="AF1">
+        <v>2054</v>
+      </c>
+      <c r="AG1">
+        <v>2055</v>
+      </c>
+      <c r="AH1">
+        <v>2056</v>
+      </c>
+      <c r="AI1">
+        <v>2057</v>
+      </c>
+      <c r="AJ1">
+        <v>2058</v>
+      </c>
+      <c r="AK1">
+        <v>2059</v>
+      </c>
+      <c r="AL1">
+        <v>2060</v>
+      </c>
+      <c r="AM1">
+        <v>2061</v>
+      </c>
+      <c r="AN1">
+        <v>2062</v>
+      </c>
+      <c r="AO1">
+        <v>2063</v>
+      </c>
+      <c r="AP1">
+        <v>2064</v>
+      </c>
+      <c r="AQ1">
+        <v>2065</v>
+      </c>
+      <c r="AR1">
+        <v>2066</v>
+      </c>
+      <c r="AS1">
+        <v>2067</v>
+      </c>
+      <c r="AT1">
+        <v>2068</v>
+      </c>
+      <c r="AU1">
+        <v>2069</v>
+      </c>
+      <c r="AV1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="B2" s="36">
         <v>0.2</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
+      <c r="C2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="E2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="F2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="G2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="I2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="J2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="K2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="L2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="M2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="N2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="O2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="P2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="Q2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="R2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="S2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="T2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="U2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="V2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="W2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="X2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="Y2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="Z2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AA2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AB2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AC2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AD2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AE2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AF2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AG2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AH2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AI2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AJ2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AK2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AL2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AM2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AN2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AO2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AP2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AQ2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AR2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AS2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AT2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AU2" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="AV2" s="36">
+        <v>0.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
-    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEC943B8-3F3F-4620-B9E3-E6CE6F7C7DE5}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93F19D14-561A-4FAA-A5A7-50777BEEFC07}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C657E97-A41A-4F36-A557-1FF848BC353B}"/>
 </file>